--- a/cats/data/signals_asbuilt_abs_v2.xlsx
+++ b/cats/data/signals_asbuilt_abs_v2.xlsx
@@ -1256,7 +1256,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1268,7 +1268,11 @@
           <t>(9,8) RIGHT</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr"/>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Switch 5</t>
+        </is>
+      </c>
       <c r="G2" t="inlineStr">
         <is>
           <t>4</t>
@@ -1281,37 +1285,37 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>432 433</t>
+          <t>432</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>C4-OU2-1 C4-OU2-2</t>
+          <t>C4-OU2-1 C4-OU2-3 C4-OU2-2</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>track/signalhead/IH432 track/signalhead/IH433</t>
+          <t>track/signalhead/432</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>IF$shsm:AAR-1946:SL-2-high-abs(IH432)(IH433)</t>
+          <t>IF$shsm:AAR-1946:SL-1-low(IH432)</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>double</t>
+          <t>single</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>hart-aar SL-2-digicon</t>
+          <t>AAR-1946 SL-1-low (3-pin STOP/APPROACH/CLEAR)</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>LCOS Signal 0 UID 32; Digicon mast '6LB'</t>
+          <t>LCOS Signal 0 UID 32; STOP/APPROACH/CLEAR; lamp G; was S3-6 G/Y/R</t>
         </is>
       </c>
     </row>
@@ -1339,7 +1343,11 @@
           <t>(9,7) RIGHT</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr"/>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Switch 5</t>
+        </is>
+      </c>
       <c r="G3" t="inlineStr">
         <is>
           <t>4</t>
@@ -1357,12 +1365,12 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>C4-OU2-3</t>
+          <t>C4-OU2-4 C4-OU2-6 C4-OU2-5</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>track/signalhead/IH434</t>
+          <t>track/signalhead/434</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -1377,12 +1385,12 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>AAR-1946 SL-1-low</t>
+          <t>AAR-1946 SL-1-low (3-pin STOP/APPROACH/CLEAR)</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>LCOS Signal 2 UID 34; Digicon mast '6LA' (1-head; was Top of 2-head)</t>
+          <t>LCOS Signal 2 UID 34; STOP/APPROACH/CLEAR; lamp G; was S3-7 G/Y/R</t>
         </is>
       </c>
     </row>
@@ -1410,7 +1418,11 @@
           <t>(4,3) LEFT</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr"/>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Switch 3</t>
+        </is>
+      </c>
       <c r="G4" t="inlineStr">
         <is>
           <t>4</t>
@@ -1428,12 +1440,12 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>C4-OU2-5</t>
+          <t>C4-OU3-4 C4-OU3-6 C4-OU3-5</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>track/signalhead/IH436</t>
+          <t>track/signalhead/436</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -1448,12 +1460,12 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>AAR-1946 SL-1-low</t>
+          <t>AAR-1946 SL-1-low (3-pin STOP/APPROACH/CLEAR)</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>LCOS Signal 4 UID 36; Digicon mast '4RA'</t>
+          <t>LCOS Signal 4 UID 36; STOP/APPROACH/CLEAR; lamp G; was S3-9 G/Y/R</t>
         </is>
       </c>
     </row>
@@ -1481,7 +1493,11 @@
           <t>(4,4) LEFT</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr"/>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Switch 3</t>
+        </is>
+      </c>
       <c r="G5" t="inlineStr">
         <is>
           <t>4</t>
@@ -1499,12 +1515,12 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>C4-OU2-6</t>
+          <t>C4-OU3-7 C4-OU3-8 C4-OU2-7</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>track/signalhead/IH437</t>
+          <t>track/signalhead/437</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1519,12 +1535,12 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>AAR-1946 SL-1-low</t>
+          <t>AAR-1946 SL-1-low (3-pin STOP/APPROACH/CLEAR)</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>LCOS Signal 5 UID 37; Digicon mast '4RB'</t>
+          <t>LCOS Signal 5 UID 37; STOP/APPROACH/CLEAR; lamp G; was S3-11 G/Y/R (Y on OU2-7)</t>
         </is>
       </c>
     </row>
@@ -1540,7 +1556,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1552,7 +1568,11 @@
           <t>(8,3) RIGHT</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr"/>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Switch 1</t>
+        </is>
+      </c>
       <c r="G6" t="inlineStr">
         <is>
           <t>4</t>
@@ -1565,44 +1585,44 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>438 439</t>
+          <t>438</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>C4-OU3-1 C4-OU3-2</t>
+          <t>C4-OU3-1 C4-OU3-3 C4-OU3-2</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>track/signalhead/IH438 track/signalhead/IH439</t>
+          <t>track/signalhead/438</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>IF$shsm:AAR-1946:SL-2-high-abs(IH438)(IH439)</t>
+          <t>IF$shsm:AAR-1946:SL-1-low(IH438)</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>double</t>
+          <t>single</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>hart-aar SL-2-digicon</t>
+          <t>AAR-1946 SL-1-low (3-pin STOP/APPROACH/CLEAR)</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>LCOS Signal 6 UID 38; Digicon mast '2L'</t>
+          <t>LCOS Signal 6 UID 38; STOP/APPROACH/CLEAR; lamp G; was S3-8 G/Y/R</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>OS Barn</t>
+          <t>Track Barn</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1611,7 +1631,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1623,7 +1643,11 @@
           <t>(12,7) LEFT</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr"/>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Switch 7</t>
+        </is>
+      </c>
       <c r="G7" t="inlineStr">
         <is>
           <t>13</t>
@@ -1631,54 +1655,54 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>C1</t>
+          <t>C5</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1332 1333</t>
+          <t>1332</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>C1-OU2-1 C1-OU2-2</t>
+          <t>C5-OU1-1 C5-OU1-3 C5-OU1-2</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>track/signalhead/IH1332 track/signalhead/IH1333</t>
+          <t>track/signalhead/1332</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>IF$shsm:AAR-1946:SL-2-high-abs(IH1332)(IH1333)</t>
+          <t>IF$shsm:AAR-1946:SL-1-low(IH1332)</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>double</t>
+          <t>single</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>hart-aar SL-2-digicon</t>
+          <t>AAR-1946 SL-1-low (3-pin STOP/APPROACH/CLEAR)</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>LCOS Signal 0 UID 32; Digicon mast '8RA'</t>
+          <t>LCOS Signal 0 UID 32; STOP/APPROACH/CLEAR; lamp G; was S3-10 G/Y/R</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>OS Barn</t>
+          <t>Track Barn</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Mast 8LB</t>
+          <t>Mast 8RB</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -1686,15 +1710,19 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>(14,7) RIGHT</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr"/>
+          <t>(12,8) LEFT</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Switch 7</t>
+        </is>
+      </c>
       <c r="G8" t="inlineStr">
         <is>
           <t>13</t>
@@ -1702,27 +1730,27 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>C1</t>
+          <t>C5</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1334</t>
+          <t>1335</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>C1-OU2-3</t>
+          <t>C5-OU1-4 C5-OU1-5 C5-OU1-6</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>track/signalhead/IH1334</t>
+          <t>track/signalhead/1335</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>IF$shsm:AAR-1946:SL-1-low(IH1334)</t>
+          <t>IF$shsm:AAR-1946:SL-1-low(IH1335)</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -1732,40 +1760,44 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>AAR-1946 SL-1-low</t>
+          <t>AAR-1946 SL-1-low (3-pin STOP/APPROACH/CLEAR)</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>LCOS Signal 2 UID 34; Digicon mast '8LB'</t>
+          <t>LCOS Signal 3 UID 35; STOP/APPROACH/CLEAR; lamp G; was S3-12 G/R/Y silk</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>OS Barn</t>
+          <t>Track Barn</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Mast 8RB</t>
+          <t>Mast 8LB</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>(12,8) LEFT</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr"/>
+          <t>(14,7) RIGHT</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Switch 7</t>
+        </is>
+      </c>
       <c r="G9" t="inlineStr">
         <is>
           <t>13</t>
@@ -1773,49 +1805,49 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>C1</t>
+          <t>C5</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1335 1336</t>
+          <t>1334</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>C1-OU2-4 C1-OU2-5</t>
+          <t>C5-OU2-1 C5-OU2-3 C5-OU2-2</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>track/signalhead/IH1335 track/signalhead/IH1336</t>
+          <t>track/signalhead/1334</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>IF$shsm:AAR-1946:SL-2-high-abs(IH1335)(IH1336)</t>
+          <t>IF$shsm:AAR-1946:SL-1-low(IH1334)</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>double</t>
+          <t>single</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>hart-aar SL-2-digicon</t>
+          <t>AAR-1946 SL-1-low (3-pin STOP/APPROACH/CLEAR)</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>LCOS Signal 3 UID 35; Digicon mast '8RB'</t>
+          <t>LCOS Signal 2 UID 34; STOP/APPROACH/CLEAR; lamp G; was S3-4 G/Y/R</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>OS Barn</t>
+          <t>Track Barn</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1824,7 +1856,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1836,7 +1868,11 @@
           <t>(14,8) RIGHT</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr"/>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Switch 7</t>
+        </is>
+      </c>
       <c r="G10" t="inlineStr">
         <is>
           <t>13</t>
@@ -1844,42 +1880,42 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>C1</t>
+          <t>C5</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1337 1338</t>
+          <t>1337</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>C1-OU2-6 C1-OU3-1</t>
+          <t>C5-OU2-4 C5-OU2-6 C5-OU2-5</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>track/signalhead/IH1337 track/signalhead/IH1338</t>
+          <t>track/signalhead/1337</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>IF$shsm:AAR-1946:SL-2-high-abs(IH1337)(IH1338)</t>
+          <t>IF$shsm:AAR-1946:SL-1-low(IH1337)</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>double</t>
+          <t>single</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>hart-aar SL-2-digicon</t>
+          <t>AAR-1946 SL-1-low (3-pin STOP/APPROACH/CLEAR)</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>LCOS Signal 5 UID 37; Digicon mast '8LA'</t>
+          <t>LCOS Signal 5 UID 37; STOP/APPROACH/CLEAR; lamp G; was S3-5 G/Y/R</t>
         </is>
       </c>
     </row>
@@ -1895,7 +1931,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1907,50 +1943,54 @@
           <t>(28,6) LEFT</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr"/>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Switch 23</t>
+        </is>
+      </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>C7</t>
+          <t>C3</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1232 1233</t>
+          <t>232</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>C7-OU2-1 C7-OU2-2</t>
+          <t>C3-OU1-1 C3-OU1-3 C3-OU1-2</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>track/signalhead/IH1232 track/signalhead/IH1233</t>
+          <t>track/signalhead/232</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>IF$shsm:AAR-1946:SL-2-high-abs(IH1232)(IH1233)</t>
+          <t>IF$shsm:AAR-1946:SL-1-low(IH232)</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>double</t>
+          <t>single</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>hart-aar SL-2-digicon</t>
+          <t>AAR-1946 SL-1-low (3-pin STOP/APPROACH/CLEAR)</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>LCOS Signal 0 UID 32; Digicon mast '24RA'</t>
+          <t>LCOS Signal 0 UID 32; STOP/APPROACH/CLEAR; lamp G; was C3-OU1 new 5V</t>
         </is>
       </c>
     </row>
@@ -1966,7 +2006,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1978,50 +2018,54 @@
           <t>(30,6) RIGHT</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr"/>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Switch 23</t>
+        </is>
+      </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>C7</t>
+          <t>C3</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1234 1235</t>
+          <t>233</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>C7-OU2-3 C7-OU2-4</t>
+          <t>C3-OU1-4 C3-OU1-6 C3-OU1-5</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>track/signalhead/IH1234 track/signalhead/IH1235</t>
+          <t>track/signalhead/233</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>IF$shsm:AAR-1946:SL-2-high-abs(IH1234)(IH1235)</t>
+          <t>IF$shsm:AAR-1946:SL-1-low(IH233)</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>double</t>
+          <t>single</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>hart-aar SL-2-digicon</t>
+          <t>AAR-1946 SL-1-low (3-pin STOP/APPROACH/CLEAR)</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>LCOS Signal 2 UID 34; Digicon mast '24L'</t>
+          <t>LCOS Signal 1 UID 33; STOP/APPROACH/CLEAR; lamp G; was C3-OU1 new 5V</t>
         </is>
       </c>
     </row>
@@ -2049,35 +2093,39 @@
           <t>(28,7) LEFT</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr"/>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Switch 23</t>
+        </is>
+      </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>C7</t>
+          <t>C3</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>1236</t>
+          <t>234</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>C7-OU2-5</t>
+          <t>C3-OU1-7 C3-OU2-1 C3-OU1-8</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>track/signalhead/IH1236</t>
+          <t>track/signalhead/234</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>IF$shsm:AAR-1946:SL-1-low(IH1236)</t>
+          <t>IF$shsm:AAR-1946:SL-1-low(IH234)</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -2087,12 +2135,12 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>AAR-1946 SL-1-low</t>
+          <t>AAR-1946 SL-1-low (3-pin STOP/APPROACH/CLEAR)</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>LCOS Signal 4 UID 36; Digicon mast '24RB'</t>
+          <t>LCOS Signal 2 UID 34; STOP/APPROACH/CLEAR; lamp G; was OU1-7/8 + OU2-1</t>
         </is>
       </c>
     </row>
@@ -2108,7 +2156,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2120,50 +2168,54 @@
           <t>(34,7) RIGHT</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr"/>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Switch 33</t>
+        </is>
+      </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>C7</t>
+          <t>C3</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>1237 1238</t>
+          <t>235</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>C7-OU2-6 C7-OU3-1</t>
+          <t>C3-OU2-2 C3-OU2-4 C3-OU2-3</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>track/signalhead/IH1237 track/signalhead/IH1238</t>
+          <t>track/signalhead/235</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>IF$shsm:AAR-1946:SL-2-high-abs(IH1237)(IH1238)</t>
+          <t>IF$shsm:AAR-1946:SL-1-low(IH235)</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>double</t>
+          <t>single</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>hart-aar SL-2-digicon</t>
+          <t>AAR-1946 SL-1-low (3-pin STOP/APPROACH/CLEAR)</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>LCOS Signal 5 UID 37; Digicon mast '34L'</t>
+          <t>LCOS Signal 3 UID 35; STOP/APPROACH/CLEAR; lamp G; was was S2-5/S2-3 mix</t>
         </is>
       </c>
     </row>
@@ -2191,35 +2243,39 @@
           <t>(31,7) BOTTOM</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr"/>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Switch 31</t>
+        </is>
+      </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>C7</t>
+          <t>C3</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>1239</t>
+          <t>236</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>C7-OU3-2</t>
+          <t>C3-OU2-5 C3-OU2-7 C3-OU2-6</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>track/signalhead/IH1239</t>
+          <t>track/signalhead/236</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>IF$shsm:AAR-1946:SL-1-low(IH1239)</t>
+          <t>IF$shsm:AAR-1946:SL-1-low(IH236)</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -2229,12 +2285,12 @@
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>AAR-1946 SL-1-low</t>
+          <t>AAR-1946 SL-1-low (3-pin STOP/APPROACH/CLEAR)</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>LCOS Signal 7 UID 39; Digicon mast '32R'</t>
+          <t>LCOS Signal 4 UID 36; STOP/APPROACH/CLEAR; lamp G; was OU2-8 is relay</t>
         </is>
       </c>
     </row>
@@ -2250,7 +2306,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2262,50 +2318,54 @@
           <t>(33,8) LEFT</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr"/>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Switch 33</t>
+        </is>
+      </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>C7</t>
+          <t>C3</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>1240 1241</t>
+          <t>237</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>C7-OU3-3 C7-OU3-4</t>
+          <t>C3-OU3-1 C3-OU3-3 C3-OU3-2</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>track/signalhead/IH1240 track/signalhead/IH1241</t>
+          <t>track/signalhead/237</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>IF$shsm:AAR-1946:SL-2-high-abs(IH1240)(IH1241)</t>
+          <t>IF$shsm:AAR-1946:SL-1-low(IH237)</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>double</t>
+          <t>single</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>hart-aar SL-2-digicon</t>
+          <t>AAR-1946 SL-1-low (3-pin STOP/APPROACH/CLEAR)</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>LCOS Signal 8 UID 40; Digicon mast '34R'</t>
+          <t>LCOS Signal 5 UID 37; STOP/APPROACH/CLEAR; lamp G; was was S4-6 G/R/Y</t>
         </is>
       </c>
     </row>
@@ -2321,7 +2381,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2333,7 +2393,11 @@
           <t>(43,5) RIGHT</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr"/>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Switch 39</t>
+        </is>
+      </c>
       <c r="G17" t="inlineStr">
         <is>
           <t>1</t>
@@ -2341,42 +2405,42 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>D1</t>
+          <t>C1</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>132 133</t>
+          <t>132</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>D1-OU2-1 D1-OU2-2</t>
+          <t>C1-OU2-1 C1-OU2-3 C1-OU2-2</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>track/signalhead/IH132 track/signalhead/IH133</t>
+          <t>track/signalhead/132</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>IF$shsm:AAR-1946:SL-2-high-abs(IH132)(IH133)</t>
+          <t>IF$shsm:AAR-1946:SL-1-low(IH132)</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>double</t>
+          <t>single</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>hart-aar SL-2-digicon</t>
+          <t>AAR-1946 SL-1-low (3-pin STOP/APPROACH/CLEAR)</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>LCOS Signal 0 UID 32; Digicon mast '40LB'</t>
+          <t>LCOS Signal 0 UID 32; STOP/APPROACH/CLEAR; lamp G; was S1-1 G/Y/R</t>
         </is>
       </c>
     </row>
@@ -2388,7 +2452,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Mast 2036</t>
+          <t>Mast 36RA</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -2401,10 +2465,14 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>(62,6) LEFT</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr"/>
+          <t>(37,6) LEFT</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Switch 35</t>
+        </is>
+      </c>
       <c r="G18" t="inlineStr">
         <is>
           <t>1</t>
@@ -2412,27 +2480,27 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>D1</t>
+          <t>C1</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>134</t>
+          <t>135</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>D1-OU2-3</t>
+          <t>C1-OU2-4 C1-OU2-6 C1-OU2-5</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>track/signalhead/IH134</t>
+          <t>track/signalhead/135</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>IF$shsm:AAR-1946:SL-1-low(IH134)</t>
+          <t>IF$shsm:AAR-1946:SL-1-low(IH135)</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -2442,12 +2510,12 @@
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>AAR-1946 SL-1-low</t>
+          <t>AAR-1946 SL-1-low (3-pin STOP/APPROACH/CLEAR)</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>LCOS Signal 2 UID 34; Digicon mast '2036'</t>
+          <t>LCOS Signal 3 UID 35; STOP/APPROACH/CLEAR; lamp G; was S1-2 G/Y/R</t>
         </is>
       </c>
     </row>
@@ -2459,23 +2527,27 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Mast 36RA</t>
+          <t>Mast 38LB</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>(37,6) LEFT</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr"/>
+          <t>(43,8) RIGHT</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Switch 37</t>
+        </is>
+      </c>
       <c r="G19" t="inlineStr">
         <is>
           <t>1</t>
@@ -2483,42 +2555,42 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>D1</t>
+          <t>C1</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>135 136</t>
+          <t>139</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>D1-OU2-4 D1-OU2-5</t>
+          <t>C1-OU3-1 C1-OU3-3 C1-OU3-2</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>track/signalhead/IH135 track/signalhead/IH136</t>
+          <t>track/signalhead/139</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>IF$shsm:AAR-1946:SL-2-high-abs(IH135)(IH136)</t>
+          <t>IF$shsm:AAR-1946:SL-1-low(IH139)</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>double</t>
+          <t>single</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>hart-aar SL-2-digicon</t>
+          <t>AAR-1946 SL-1-low (3-pin STOP/APPROACH/CLEAR)</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>LCOS Signal 3 UID 35; Digicon mast '36RA'</t>
+          <t>LCOS Signal 7 UID 39; STOP/APPROACH/CLEAR; lamp G; was S1-3 G/Y/R</t>
         </is>
       </c>
     </row>
@@ -2530,11 +2602,11 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Mast 36RB</t>
+          <t>Mast 40LA</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2543,10 +2615,14 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>(37,7) LEFT</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr"/>
+          <t>(43,6) RIGHT</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Switch 39</t>
+        </is>
+      </c>
       <c r="G20" t="inlineStr">
         <is>
           <t>1</t>
@@ -2554,42 +2630,42 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>D1</t>
+          <t>C1</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>137 138</t>
+          <t>142</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>D1-OU2-6 D1-OU2-7</t>
+          <t>C1-OU3-4 C1-OU3-6 C1-OU3-5</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>track/signalhead/IH137 track/signalhead/IH138</t>
+          <t>track/signalhead/142</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>IF$shsm:AAR-1946:SL-2-high-abs(IH137)(IH138)</t>
+          <t>IF$shsm:AAR-1946:SL-1-low(IH142)</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>double</t>
+          <t>single</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>hart-aar SL-2-digicon</t>
+          <t>AAR-1946 SL-1-low (3-pin STOP/APPROACH/CLEAR)</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>LCOS Signal 5 UID 37; Digicon mast '36RB'</t>
+          <t>LCOS Signal 10 UID 42; STOP/APPROACH/CLEAR; lamp G; was S1-4 G/Y/R</t>
         </is>
       </c>
     </row>
@@ -2601,23 +2677,27 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Mast 38LB</t>
+          <t>Mast 38LA</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>(43,8) RIGHT</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr"/>
+          <t>(43,7) RIGHT</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Switch 37</t>
+        </is>
+      </c>
       <c r="G21" t="inlineStr">
         <is>
           <t>1</t>
@@ -2625,42 +2705,42 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>D1</t>
+          <t>C1</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>139 140</t>
+          <t>143</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>D1-OU2-8 D1-OU3-1</t>
+          <t>C1-OU2-7 C1-OU3-8 C1-OU3-7</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>track/signalhead/IH139 track/signalhead/IH140</t>
+          <t>track/signalhead/143</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>IF$shsm:AAR-1946:SL-2-high-abs(IH139)(IH140)</t>
+          <t>IF$shsm:AAR-1946:SL-1-low(IH143)</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>double</t>
+          <t>single</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>hart-aar SL-2-digicon</t>
+          <t>AAR-1946 SL-1-low (3-pin STOP/APPROACH/CLEAR)</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>LCOS Signal 7 UID 39; Digicon mast '38LB'</t>
+          <t>LCOS Signal 11 UID 43; STOP/APPROACH/CLEAR; lamp G; was spares G/Y/R</t>
         </is>
       </c>
     </row>
@@ -2672,7 +2752,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Mast 2035</t>
+          <t>Mast 36RB</t>
         </is>
       </c>
       <c r="C22" t="n">
@@ -2680,43 +2760,47 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>(61,6) RIGHT</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr"/>
+          <t>(37,7) LEFT</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Switch 35</t>
+        </is>
+      </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>D1</t>
+          <t>C7</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>141</t>
+          <t>1132</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>D1-OU3-2</t>
+          <t>C7-OU2-1 C7-OU2-2 C7-OU2-3</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>track/signalhead/IH141</t>
+          <t>track/signalhead/1132</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>IF$shsm:AAR-1946:SL-1-low(IH141)</t>
+          <t>IF$shsm:AAR-1946:SL-1-low(IH1132)</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -2726,12 +2810,12 @@
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>AAR-1946 SL-1-low</t>
+          <t>AAR-1946 SL-1-low (3-pin STOP/APPROACH/CLEAR)</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>LCOS Signal 9 UID 41; Digicon mast '2035'</t>
+          <t>LCOS Signal 0 UID 32; STOP/APPROACH/CLEAR; lamp G; was S1-5 G/R/Y silk</t>
         </is>
       </c>
     </row>
@@ -2743,7 +2827,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Mast 40LA</t>
+          <t>Mast 2036</t>
         </is>
       </c>
       <c r="C23" t="n">
@@ -2756,38 +2840,38 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>(43,6) RIGHT</t>
+          <t>(62,6) LEFT</t>
         </is>
       </c>
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>D1</t>
+          <t>C7</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>142</t>
+          <t>1133</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>D1-OU3-3</t>
+          <t>C7-OU2-4 C7-OU2-5 C7-OU2-6</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>track/signalhead/IH142</t>
+          <t>track/signalhead/1133</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>IF$shsm:AAR-1946:SL-1-low(IH142)</t>
+          <t>IF$shsm:AAR-1946:SL-1-low(IH1133)</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -2797,12 +2881,12 @@
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>AAR-1946 SL-1-low</t>
+          <t>AAR-1946 SL-1-low (3-pin STOP/APPROACH/CLEAR)</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>LCOS Signal 10 UID 42; Digicon mast '40LA'</t>
+          <t>LCOS Signal 1 UID 33; STOP/APPROACH/CLEAR; lamp G; was S1-6 G/R/Y silk</t>
         </is>
       </c>
     </row>
@@ -2814,7 +2898,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Mast 38LA</t>
+          <t>Mast 2035</t>
         </is>
       </c>
       <c r="C24" t="n">
@@ -2822,43 +2906,43 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>(43,7) RIGHT</t>
+          <t>(61,6) RIGHT</t>
         </is>
       </c>
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>D1</t>
+          <t>C7</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>143</t>
+          <t>1134</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>D1-OU3-4</t>
+          <t>C7-OU3-1 C7-OU3-2 C7-OU3-3</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>track/signalhead/IH143</t>
+          <t>track/signalhead/1134</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>IF$shsm:AAR-1946:SL-1-low(IH143)</t>
+          <t>IF$shsm:AAR-1946:SL-1-low(IH1134)</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -2868,12 +2952,12 @@
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>AAR-1946 SL-1-low</t>
+          <t>AAR-1946 SL-1-low (3-pin STOP/APPROACH/CLEAR)</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>LCOS Signal 11 UID 43; Digicon mast '38LA'</t>
+          <t>LCOS Signal 2 UID 34; STOP/APPROACH/CLEAR; lamp G; was S4-6 G/R/Y silk</t>
         </is>
       </c>
     </row>
@@ -3063,7 +3147,7 @@
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>OS 1</t>
+          <t>OS Switch 1</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
@@ -3073,17 +3157,17 @@
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>OS W-1</t>
+          <t>Track W-1</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>OS 1</t>
+          <t>OS Switch 1</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
-          <t>OS 3+W-1</t>
+          <t>OS Switch 3+W-1</t>
         </is>
       </c>
       <c r="I2" s="3" t="inlineStr">
@@ -3150,7 +3234,7 @@
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>OS 1</t>
+          <t>OS Switch 1</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
@@ -3160,17 +3244,17 @@
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>OS W-1</t>
+          <t>Track W-1</t>
         </is>
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>OS 1</t>
+          <t>OS Switch 1</t>
         </is>
       </c>
       <c r="H3" s="3" t="inlineStr">
         <is>
-          <t>OS 3+W-1</t>
+          <t>OS Switch 3+W-1</t>
         </is>
       </c>
       <c r="I3" s="3" t="inlineStr">
@@ -3241,7 +3325,7 @@
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>OS 1</t>
+          <t>OS Switch 1</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
@@ -3251,17 +3335,17 @@
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>OS W-1</t>
+          <t>Track W-1</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>OS 1</t>
+          <t>OS Switch 1</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>OS 3+W-1</t>
+          <t>OS Switch 3+W-1</t>
         </is>
       </c>
       <c r="I4" s="3" t="inlineStr">
@@ -3332,7 +3416,7 @@
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>OS 1</t>
+          <t>OS Switch 1</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
@@ -3342,17 +3426,17 @@
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>OS W-2</t>
+          <t>Track W-2</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>OS 1</t>
+          <t>OS Switch 1</t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>OS 3+W-2</t>
+          <t>OS Switch 3+W-2</t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr">
@@ -3419,7 +3503,7 @@
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>OS 1</t>
+          <t>OS Switch 1</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
@@ -3429,17 +3513,17 @@
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>OS W-2</t>
+          <t>Track W-2</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>OS 1</t>
+          <t>OS Switch 1</t>
         </is>
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
-          <t>OS 3+W-2</t>
+          <t>OS Switch 3+W-2</t>
         </is>
       </c>
       <c r="I6" s="3" t="inlineStr">
@@ -3510,7 +3594,7 @@
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>OS 1</t>
+          <t>OS Switch 1</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
@@ -3520,17 +3604,17 @@
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>OS W-2</t>
+          <t>Track W-2</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>OS 1</t>
+          <t>OS Switch 1</t>
         </is>
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t>OS 3+W-2</t>
+          <t>OS Switch 3+W-2</t>
         </is>
       </c>
       <c r="I7" s="3" t="inlineStr">
@@ -3601,7 +3685,7 @@
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>OS 1</t>
+          <t>OS Switch 1</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
@@ -3616,12 +3700,12 @@
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>OS 1</t>
+          <t>OS Switch 1</t>
         </is>
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t>OS Brick-Plane + OS 102</t>
+          <t>Track Brick-Plane + OS 102</t>
         </is>
       </c>
       <c r="I8" s="3" t="inlineStr">
@@ -3684,7 +3768,7 @@
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>OS 1</t>
+          <t>OS Switch 1</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
@@ -3699,12 +3783,12 @@
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>OS 1</t>
+          <t>OS Switch 1</t>
         </is>
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t>OS Brick-Plane + OS 102</t>
+          <t>Track Brick-Plane + OS 102</t>
         </is>
       </c>
       <c r="I9" s="3" t="inlineStr">
@@ -3771,7 +3855,7 @@
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>OS 1</t>
+          <t>OS Switch 1</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
@@ -3786,12 +3870,12 @@
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>OS 1</t>
+          <t>OS Switch 1</t>
         </is>
       </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
-          <t>OS Brick-Plane + OS 102</t>
+          <t>Track Brick-Plane + OS 102</t>
         </is>
       </c>
       <c r="I10" s="3" t="inlineStr">
@@ -3858,12 +3942,12 @@
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>OS 3</t>
+          <t>OS Switch 3</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>OS W-1</t>
+          <t>Track W-1</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
@@ -3873,12 +3957,12 @@
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>OS 3</t>
+          <t>OS Switch 3</t>
         </is>
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t>OS 1</t>
+          <t>OS Switch 1</t>
         </is>
       </c>
       <c r="I11" s="3" t="inlineStr">
@@ -3945,12 +4029,12 @@
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>OS 3</t>
+          <t>OS Switch 3</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>OS W-1</t>
+          <t>Track W-1</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
@@ -3960,12 +4044,12 @@
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>OS 3</t>
+          <t>OS Switch 3</t>
         </is>
       </c>
       <c r="H12" s="3" t="inlineStr">
         <is>
-          <t>OS 1</t>
+          <t>OS Switch 1</t>
         </is>
       </c>
       <c r="I12" s="3" t="inlineStr">
@@ -4036,12 +4120,12 @@
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>OS 3</t>
+          <t>OS Switch 3</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>OS W-1</t>
+          <t>Track W-1</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
@@ -4051,12 +4135,12 @@
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>OS 3</t>
+          <t>OS Switch 3</t>
         </is>
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t>OS 1</t>
+          <t>OS Switch 1</t>
         </is>
       </c>
       <c r="I13" s="3" t="inlineStr">
@@ -4127,12 +4211,12 @@
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>OS 3</t>
+          <t>OS Switch 3</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>OS W-2</t>
+          <t>Track W-2</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
@@ -4142,12 +4226,12 @@
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>OS 3</t>
+          <t>OS Switch 3</t>
         </is>
       </c>
       <c r="H14" s="3" t="inlineStr">
         <is>
-          <t>OS 1</t>
+          <t>OS Switch 1</t>
         </is>
       </c>
       <c r="I14" s="3" t="inlineStr">
@@ -4214,12 +4298,12 @@
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>OS 3</t>
+          <t>OS Switch 3</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>OS W-2</t>
+          <t>Track W-2</t>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
@@ -4229,12 +4313,12 @@
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>OS 3</t>
+          <t>OS Switch 3</t>
         </is>
       </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
-          <t>OS 1</t>
+          <t>OS Switch 1</t>
         </is>
       </c>
       <c r="I15" s="3" t="inlineStr">
@@ -4305,12 +4389,12 @@
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>OS 3</t>
+          <t>OS Switch 3</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>OS W-2</t>
+          <t>Track W-2</t>
         </is>
       </c>
       <c r="F16" s="3" t="inlineStr">
@@ -4320,12 +4404,12 @@
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>OS 3</t>
+          <t>OS Switch 3</t>
         </is>
       </c>
       <c r="H16" s="3" t="inlineStr">
         <is>
-          <t>OS 1</t>
+          <t>OS Switch 1</t>
         </is>
       </c>
       <c r="I16" s="3" t="inlineStr">
@@ -4396,12 +4480,12 @@
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>OS W-1</t>
+          <t>Track W-1</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>OS W-1</t>
+          <t>Track W-1</t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
@@ -4411,7 +4495,7 @@
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>OS W-1</t>
+          <t>Track W-1</t>
         </is>
       </c>
       <c r="H17" s="3" t="inlineStr"/>
@@ -4471,12 +4555,12 @@
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>OS W-2</t>
+          <t>Track W-2</t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>OS W-2</t>
+          <t>Track W-2</t>
         </is>
       </c>
       <c r="F18" s="3" t="inlineStr">
@@ -4486,7 +4570,7 @@
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>OS W-2</t>
+          <t>Track W-2</t>
         </is>
       </c>
       <c r="H18" s="3" t="inlineStr"/>
@@ -4714,12 +4798,12 @@
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>OS 5</t>
+          <t>OS Switch 5</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>OS Scale / Brick shaft</t>
+          <t>Track Scale / Brick shaft</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
@@ -4729,12 +4813,12 @@
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>OS 5</t>
+          <t>OS Switch 5</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
-          <t>OS Scale or East Main path</t>
+          <t>Track Scale or East Main path</t>
         </is>
       </c>
       <c r="I2" s="3" t="inlineStr">
@@ -4775,7 +4859,7 @@
       </c>
       <c r="Y2" s="3" t="inlineStr">
         <is>
-          <t>Eastbound on OS Scale / main side of Plane. Adjust N/R if field frog is opposite.</t>
+          <t>Eastbound on Track Scale / main side of Plane. Adjust N/R if field frog is opposite.</t>
         </is>
       </c>
     </row>
@@ -4797,12 +4881,12 @@
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>OS 5</t>
+          <t>OS Switch 5</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>OS Scale / Brick shaft</t>
+          <t>Track Scale / Brick shaft</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
@@ -4812,12 +4896,12 @@
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>OS 5</t>
+          <t>OS Switch 5</t>
         </is>
       </c>
       <c r="H3" s="3" t="inlineStr">
         <is>
-          <t>OS Scale or East Main path</t>
+          <t>Track Scale or East Main path</t>
         </is>
       </c>
       <c r="I3" s="3" t="inlineStr">
@@ -4862,7 +4946,7 @@
       </c>
       <c r="Y3" s="3" t="inlineStr">
         <is>
-          <t>Eastbound on OS Scale / main side of Plane. Adjust N/R if field frog is opposite.</t>
+          <t>Eastbound on Track Scale / main side of Plane. Adjust N/R if field frog is opposite.</t>
         </is>
       </c>
     </row>
@@ -4884,12 +4968,12 @@
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>OS 5</t>
+          <t>OS Switch 5</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>OS Scale / Brick shaft</t>
+          <t>Track Scale / Brick shaft</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
@@ -4899,12 +4983,12 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>OS 5</t>
+          <t>OS Switch 5</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>OS Scale or East Main path</t>
+          <t>Track Scale or East Main path</t>
         </is>
       </c>
       <c r="I4" s="3" t="inlineStr">
@@ -4949,7 +5033,7 @@
       </c>
       <c r="Y4" s="3" t="inlineStr">
         <is>
-          <t>Eastbound on OS Scale / main side of Plane. Adjust N/R if field frog is opposite.</t>
+          <t>Eastbound on Track Scale / main side of Plane. Adjust N/R if field frog is opposite.</t>
         </is>
       </c>
     </row>
@@ -4971,7 +5055,7 @@
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>OS 5</t>
+          <t>OS Switch 5</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
@@ -4986,7 +5070,7 @@
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>OS 5</t>
+          <t>OS Switch 5</t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
@@ -5054,7 +5138,7 @@
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>OS 5</t>
+          <t>OS Switch 5</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
@@ -5069,7 +5153,7 @@
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>OS 5</t>
+          <t>OS Switch 5</t>
         </is>
       </c>
       <c r="H6" s="3" t="inlineStr">
@@ -5141,7 +5225,7 @@
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>OS 5</t>
+          <t>OS Switch 5</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
@@ -5156,7 +5240,7 @@
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>OS 5</t>
+          <t>OS Switch 5</t>
         </is>
       </c>
       <c r="H7" s="3" t="inlineStr">
@@ -5396,27 +5480,27 @@
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>OS 7</t>
+          <t>OS Switch 7</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>OS Scale / Plane</t>
+          <t>Track Scale / Plane</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>OS Barn / east</t>
+          <t>Track Barn / east</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>OS 7</t>
+          <t>OS Switch 7</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
-          <t>OS Barn</t>
+          <t>Track Barn</t>
         </is>
       </c>
       <c r="I2" s="3" t="inlineStr">
@@ -5479,27 +5563,27 @@
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>OS 7</t>
+          <t>OS Switch 7</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>OS Scale / Plane</t>
+          <t>Track Scale / Plane</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>OS Barn / east</t>
+          <t>Track Barn / east</t>
         </is>
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>OS 7</t>
+          <t>OS Switch 7</t>
         </is>
       </c>
       <c r="H3" s="3" t="inlineStr">
         <is>
-          <t>OS Barn</t>
+          <t>Track Barn</t>
         </is>
       </c>
       <c r="I3" s="3" t="inlineStr">
@@ -5566,27 +5650,27 @@
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>OS 7</t>
+          <t>OS Switch 7</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>OS Scale / Plane</t>
+          <t>Track Scale / Plane</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>OS Barn / east</t>
+          <t>Track Barn / east</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>OS 7</t>
+          <t>OS Switch 7</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>OS Barn</t>
+          <t>Track Barn</t>
         </is>
       </c>
       <c r="I4" s="3" t="inlineStr">
@@ -5653,12 +5737,12 @@
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>OS 7</t>
+          <t>OS Switch 7</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>OS Barn</t>
+          <t>Track Barn</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
@@ -5668,12 +5752,12 @@
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>OS 7</t>
+          <t>OS Switch 7</t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>OS Scale</t>
+          <t>Track Scale</t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr">
@@ -5736,12 +5820,12 @@
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>OS 7</t>
+          <t>OS Switch 7</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>OS Barn</t>
+          <t>Track Barn</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
@@ -5751,12 +5835,12 @@
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>OS 7</t>
+          <t>OS Switch 7</t>
         </is>
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
-          <t>OS Scale</t>
+          <t>Track Scale</t>
         </is>
       </c>
       <c r="I6" s="3" t="inlineStr">
@@ -5823,12 +5907,12 @@
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>OS 7</t>
+          <t>OS Switch 7</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>OS Barn</t>
+          <t>Track Barn</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
@@ -5838,12 +5922,12 @@
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>OS 7</t>
+          <t>OS Switch 7</t>
         </is>
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t>OS Scale</t>
+          <t>Track Scale</t>
         </is>
       </c>
       <c r="I7" s="3" t="inlineStr">
@@ -5910,7 +5994,7 @@
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>OS 7b</t>
+          <t>OS Switch 7b</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
@@ -5925,7 +6009,7 @@
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>OS 7b</t>
+          <t>OS Switch 7b</t>
         </is>
       </c>
       <c r="H8" s="3" t="inlineStr">
@@ -5993,7 +6077,7 @@
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>OS 7b</t>
+          <t>OS Switch 7b</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
@@ -6008,7 +6092,7 @@
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>OS 7b</t>
+          <t>OS Switch 7b</t>
         </is>
       </c>
       <c r="H9" s="3" t="inlineStr">
@@ -6080,7 +6164,7 @@
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>OS 7b</t>
+          <t>OS Switch 7b</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
@@ -6095,7 +6179,7 @@
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>OS 7b</t>
+          <t>OS Switch 7b</t>
         </is>
       </c>
       <c r="H10" s="3" t="inlineStr">
@@ -6167,7 +6251,7 @@
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>OS 7b</t>
+          <t>OS Switch 7b</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
@@ -6182,7 +6266,7 @@
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>OS 7b</t>
+          <t>OS Switch 7b</t>
         </is>
       </c>
       <c r="H11" s="3" t="inlineStr">
@@ -6250,7 +6334,7 @@
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>OS 7b</t>
+          <t>OS Switch 7b</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
@@ -6265,7 +6349,7 @@
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>OS 7b</t>
+          <t>OS Switch 7b</t>
         </is>
       </c>
       <c r="H12" s="3" t="inlineStr">
@@ -6337,7 +6421,7 @@
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>OS 7b</t>
+          <t>OS Switch 7b</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
@@ -6352,7 +6436,7 @@
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>OS 7b</t>
+          <t>OS Switch 7b</t>
         </is>
       </c>
       <c r="H13" s="3" t="inlineStr">
@@ -6592,7 +6676,7 @@
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>OS 23a</t>
+          <t>OS Switch 23a</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
@@ -6607,7 +6691,7 @@
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>OS 23a</t>
+          <t>OS Switch 23a</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
@@ -6675,7 +6759,7 @@
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>OS 23a</t>
+          <t>OS Switch 23a</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
@@ -6690,7 +6774,7 @@
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>OS 23a</t>
+          <t>OS Switch 23a</t>
         </is>
       </c>
       <c r="H3" s="3" t="inlineStr">
@@ -6762,7 +6846,7 @@
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>OS 23a</t>
+          <t>OS Switch 23a</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
@@ -6777,7 +6861,7 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>OS 23a</t>
+          <t>OS Switch 23a</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
@@ -6849,7 +6933,7 @@
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>OS 23a</t>
+          <t>OS Switch 23a</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
@@ -6864,7 +6948,7 @@
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>OS 23a</t>
+          <t>OS Switch 23a</t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
@@ -6932,7 +7016,7 @@
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>OS 23a</t>
+          <t>OS Switch 23a</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
@@ -6947,7 +7031,7 @@
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>OS 23a</t>
+          <t>OS Switch 23a</t>
         </is>
       </c>
       <c r="H6" s="3" t="inlineStr">
@@ -7019,7 +7103,7 @@
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>OS 23a</t>
+          <t>OS Switch 23a</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
@@ -7034,7 +7118,7 @@
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>OS 23a</t>
+          <t>OS Switch 23a</t>
         </is>
       </c>
       <c r="H7" s="3" t="inlineStr">
@@ -7106,12 +7190,12 @@
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>OS 23b</t>
+          <t>OS Switch 23b</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>OS S-R</t>
+          <t>Track S-R</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
@@ -7121,7 +7205,7 @@
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>OS 23b</t>
+          <t>OS Switch 23b</t>
         </is>
       </c>
       <c r="H8" s="3" t="inlineStr">
@@ -7189,12 +7273,12 @@
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>OS 23b</t>
+          <t>OS Switch 23b</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>OS S-R</t>
+          <t>Track S-R</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
@@ -7204,7 +7288,7 @@
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>OS 23b</t>
+          <t>OS Switch 23b</t>
         </is>
       </c>
       <c r="H9" s="3" t="inlineStr">
@@ -7276,12 +7360,12 @@
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>OS 23b</t>
+          <t>OS Switch 23b</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>OS S-R</t>
+          <t>Track S-R</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
@@ -7291,7 +7375,7 @@
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>OS 23b</t>
+          <t>OS Switch 23b</t>
         </is>
       </c>
       <c r="H10" s="3" t="inlineStr">
@@ -7363,7 +7447,7 @@
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>OS 33</t>
+          <t>OS Switch 33</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
@@ -7378,7 +7462,7 @@
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>OS 33</t>
+          <t>OS Switch 33</t>
         </is>
       </c>
       <c r="H11" s="3" t="inlineStr">
@@ -7446,7 +7530,7 @@
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>OS 33</t>
+          <t>OS Switch 33</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
@@ -7461,7 +7545,7 @@
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>OS 33</t>
+          <t>OS Switch 33</t>
         </is>
       </c>
       <c r="H12" s="3" t="inlineStr">
@@ -7533,7 +7617,7 @@
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>OS 33</t>
+          <t>OS Switch 33</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
@@ -7548,7 +7632,7 @@
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>OS 33</t>
+          <t>OS Switch 33</t>
         </is>
       </c>
       <c r="H13" s="3" t="inlineStr">
@@ -7620,7 +7704,7 @@
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>OS 31</t>
+          <t>OS Switch 31</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
@@ -7635,7 +7719,7 @@
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>OS 31</t>
+          <t>OS Switch 31</t>
         </is>
       </c>
       <c r="H14" s="3" t="inlineStr">
@@ -7703,7 +7787,7 @@
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>OS 31</t>
+          <t>OS Switch 31</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
@@ -7718,7 +7802,7 @@
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>OS 31</t>
+          <t>OS Switch 31</t>
         </is>
       </c>
       <c r="H15" s="3" t="inlineStr">
@@ -7790,7 +7874,7 @@
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>OS 31</t>
+          <t>OS Switch 31</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
@@ -7805,7 +7889,7 @@
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>OS 31</t>
+          <t>OS Switch 31</t>
         </is>
       </c>
       <c r="H16" s="3" t="inlineStr">
@@ -7877,7 +7961,7 @@
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>OS 33</t>
+          <t>OS Switch 33</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
@@ -7892,7 +7976,7 @@
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>OS 33</t>
+          <t>OS Switch 33</t>
         </is>
       </c>
       <c r="H17" s="3" t="inlineStr">
@@ -7960,7 +8044,7 @@
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>OS 33</t>
+          <t>OS Switch 33</t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
@@ -7975,7 +8059,7 @@
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>OS 33</t>
+          <t>OS Switch 33</t>
         </is>
       </c>
       <c r="H18" s="3" t="inlineStr">
@@ -8047,7 +8131,7 @@
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>OS 33</t>
+          <t>OS Switch 33</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
@@ -8062,7 +8146,7 @@
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>OS 33</t>
+          <t>OS Switch 33</t>
         </is>
       </c>
       <c r="H19" s="3" t="inlineStr">
@@ -8302,7 +8386,7 @@
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>OS 35b</t>
+          <t>OS Switch 35b</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
@@ -8317,12 +8401,12 @@
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>OS 35b</t>
+          <t>OS Switch 35b</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
-          <t>OS 39</t>
+          <t>OS Switch 39</t>
         </is>
       </c>
       <c r="I2" s="3" t="inlineStr">
@@ -8385,7 +8469,7 @@
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>OS 35b</t>
+          <t>OS Switch 35b</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
@@ -8400,12 +8484,12 @@
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>OS 35b</t>
+          <t>OS Switch 35b</t>
         </is>
       </c>
       <c r="H3" s="3" t="inlineStr">
         <is>
-          <t>OS 39</t>
+          <t>OS Switch 39</t>
         </is>
       </c>
       <c r="I3" s="3" t="inlineStr">
@@ -8472,7 +8556,7 @@
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>OS 35b</t>
+          <t>OS Switch 35b</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
@@ -8487,12 +8571,12 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>OS 35b</t>
+          <t>OS Switch 35b</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>OS 39</t>
+          <t>OS Switch 39</t>
         </is>
       </c>
       <c r="I4" s="3" t="inlineStr">
@@ -8559,7 +8643,7 @@
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>OS 35a</t>
+          <t>OS Switch 35a</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
@@ -8574,12 +8658,12 @@
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>OS 35a</t>
+          <t>OS Switch 35a</t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>OS 37</t>
+          <t>OS Switch 37</t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr">
@@ -8642,7 +8726,7 @@
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>OS 35a</t>
+          <t>OS Switch 35a</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
@@ -8657,12 +8741,12 @@
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>OS 35a</t>
+          <t>OS Switch 35a</t>
         </is>
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
-          <t>OS 37</t>
+          <t>OS Switch 37</t>
         </is>
       </c>
       <c r="I6" s="3" t="inlineStr">
@@ -8729,7 +8813,7 @@
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>OS 35a</t>
+          <t>OS Switch 35a</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
@@ -8744,12 +8828,12 @@
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>OS 35a</t>
+          <t>OS Switch 35a</t>
         </is>
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t>OS 37</t>
+          <t>OS Switch 37</t>
         </is>
       </c>
       <c r="I7" s="3" t="inlineStr">
@@ -8816,7 +8900,7 @@
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>OS 39</t>
+          <t>OS Switch 39</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
@@ -8831,7 +8915,7 @@
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>OS 39</t>
+          <t>OS Switch 39</t>
         </is>
       </c>
       <c r="H8" s="3" t="inlineStr">
@@ -8899,7 +8983,7 @@
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>OS 39</t>
+          <t>OS Switch 39</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
@@ -8914,7 +8998,7 @@
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>OS 39</t>
+          <t>OS Switch 39</t>
         </is>
       </c>
       <c r="H9" s="3" t="inlineStr">
@@ -8986,7 +9070,7 @@
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>OS 39</t>
+          <t>OS Switch 39</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
@@ -9001,7 +9085,7 @@
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>OS 39</t>
+          <t>OS Switch 39</t>
         </is>
       </c>
       <c r="H10" s="3" t="inlineStr">
@@ -9073,7 +9157,7 @@
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>OS 37</t>
+          <t>OS Switch 37</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
@@ -9088,7 +9172,7 @@
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>OS 37</t>
+          <t>OS Switch 37</t>
         </is>
       </c>
       <c r="H11" s="3" t="inlineStr">
@@ -9156,7 +9240,7 @@
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>OS 37</t>
+          <t>OS Switch 37</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
@@ -9171,7 +9255,7 @@
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>OS 37</t>
+          <t>OS Switch 37</t>
         </is>
       </c>
       <c r="H12" s="3" t="inlineStr">
@@ -9243,7 +9327,7 @@
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>OS 37</t>
+          <t>OS Switch 37</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
@@ -9258,7 +9342,7 @@
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>OS 37</t>
+          <t>OS Switch 37</t>
         </is>
       </c>
       <c r="H13" s="3" t="inlineStr">
@@ -9330,27 +9414,27 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>OS K-1</t>
+          <t>Track K-1</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>OS K-1</t>
+          <t>Track K-1</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>OS West Main Ext</t>
+          <t>Track West Main Ext</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>OS 39</t>
+          <t>OS Switch 39</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>OS West Main Ext</t>
+          <t>Track West Main Ext</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -9407,27 +9491,27 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>OS K-1</t>
+          <t>Track K-1</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>OS K-1</t>
+          <t>Track K-1</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>OS West Main Ext</t>
+          <t>Track West Main Ext</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>OS 39</t>
+          <t>OS Switch 39</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>OS West Main Ext</t>
+          <t>Track West Main Ext</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -9489,27 +9573,27 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>OS K-1</t>
+          <t>Track K-1</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>OS K-1</t>
+          <t>Track K-1</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>OS West Main Ext</t>
+          <t>Track West Main Ext</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>OS 39</t>
+          <t>OS Switch 39</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>OS West Main Ext</t>
+          <t>Track West Main Ext</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -9571,27 +9655,27 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>OS K-1</t>
+          <t>Track K-1</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>OS K-1</t>
+          <t>Track K-1</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>OS East Lead</t>
+          <t>Track East Lead</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>OS 39</t>
+          <t>OS Switch 39</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>OS East Lead</t>
+          <t>Track East Lead</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -9648,27 +9732,27 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>OS K-1</t>
+          <t>Track K-1</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>OS K-1</t>
+          <t>Track K-1</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>OS East Lead</t>
+          <t>Track East Lead</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>OS 39</t>
+          <t>OS Switch 39</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>OS East Lead</t>
+          <t>Track East Lead</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -9730,27 +9814,27 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>OS K-1</t>
+          <t>Track K-1</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>OS K-1</t>
+          <t>Track K-1</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>OS East Lead</t>
+          <t>Track East Lead</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>OS 39</t>
+          <t>OS Switch 39</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>OS East Lead</t>
+          <t>Track East Lead</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -9812,27 +9896,27 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>OS K-2</t>
+          <t>Track K-2</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>OS K-2</t>
+          <t>Track K-2</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>OS West Main Ext</t>
+          <t>Track West Main Ext</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>OS 37</t>
+          <t>OS Switch 37</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>OS West Main Ext</t>
+          <t>Track West Main Ext</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -9889,27 +9973,27 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>OS K-2</t>
+          <t>Track K-2</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>OS K-2</t>
+          <t>Track K-2</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>OS West Main Ext</t>
+          <t>Track West Main Ext</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>OS 37</t>
+          <t>OS Switch 37</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>OS West Main Ext</t>
+          <t>Track West Main Ext</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -9971,27 +10055,27 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>OS K-2</t>
+          <t>Track K-2</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>OS K-2</t>
+          <t>Track K-2</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>OS West Main Ext</t>
+          <t>Track West Main Ext</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>OS 37</t>
+          <t>OS Switch 37</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>OS West Main Ext</t>
+          <t>Track West Main Ext</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -10053,27 +10137,27 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>OS K-2</t>
+          <t>Track K-2</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>OS K-2</t>
+          <t>Track K-2</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>OS East Lead</t>
+          <t>Track East Lead</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>OS 37</t>
+          <t>OS Switch 37</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>OS East Lead</t>
+          <t>Track East Lead</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -10130,27 +10214,27 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>OS K-2</t>
+          <t>Track K-2</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>OS K-2</t>
+          <t>Track K-2</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>OS East Lead</t>
+          <t>Track East Lead</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>OS 37</t>
+          <t>OS Switch 37</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>OS East Lead</t>
+          <t>Track East Lead</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -10212,27 +10296,27 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>OS K-2</t>
+          <t>Track K-2</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>OS K-2</t>
+          <t>Track K-2</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>OS East Lead</t>
+          <t>Track East Lead</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>OS 37</t>
+          <t>OS Switch 37</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>OS East Lead</t>
+          <t>Track East Lead</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -10294,27 +10378,27 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>OS McKees Rocks</t>
+          <t>Track McKees Rocks</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>OS McKeesport</t>
+          <t>Track McKeesport</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>OS McKees Rocks</t>
+          <t>Track McKees Rocks</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>OS McKees Rocks</t>
+          <t>Track McKees Rocks</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>OS 39</t>
+          <t>OS Switch 39</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -10366,27 +10450,27 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>OS McKees Rocks</t>
+          <t>Track McKees Rocks</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>OS McKeesport</t>
+          <t>Track McKeesport</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>OS McKees Rocks</t>
+          <t>Track McKees Rocks</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>OS McKees Rocks</t>
+          <t>Track McKees Rocks</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>OS 39</t>
+          <t>OS Switch 39</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -10443,27 +10527,27 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>OS McKees Rocks</t>
+          <t>Track McKees Rocks</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>OS McKeesport</t>
+          <t>Track McKeesport</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>OS McKees Rocks</t>
+          <t>Track McKees Rocks</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>OS McKees Rocks</t>
+          <t>Track McKees Rocks</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>OS 39</t>
+          <t>OS Switch 39</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -10520,27 +10604,27 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>OS McKeesport</t>
+          <t>Track McKeesport</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>OS McKees Rocks</t>
+          <t>Track McKees Rocks</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>OS McKeesport</t>
+          <t>Track McKeesport</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>OS McKeesport</t>
+          <t>Track McKeesport</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>OS 37</t>
+          <t>OS Switch 37</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -10592,27 +10676,27 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>OS McKeesport</t>
+          <t>Track McKeesport</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>OS McKees Rocks</t>
+          <t>Track McKees Rocks</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>OS McKeesport</t>
+          <t>Track McKeesport</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>OS McKeesport</t>
+          <t>Track McKeesport</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>OS 37</t>
+          <t>OS Switch 37</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -10669,27 +10753,27 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>OS McKeesport</t>
+          <t>Track McKeesport</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>OS McKees Rocks</t>
+          <t>Track McKees Rocks</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>OS McKeesport</t>
+          <t>Track McKeesport</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>OS McKeesport</t>
+          <t>Track McKeesport</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>OS 37</t>
+          <t>OS Switch 37</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -10914,7 +10998,7 @@
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>OS 1</t>
+          <t>OS Switch 1</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
@@ -10924,17 +11008,17 @@
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>OS W-1</t>
+          <t>Track W-1</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>OS 1</t>
+          <t>OS Switch 1</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
-          <t>OS 3+W-1</t>
+          <t>OS Switch 3+W-1</t>
         </is>
       </c>
       <c r="I2" s="3" t="inlineStr">
@@ -11001,7 +11085,7 @@
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>OS 1</t>
+          <t>OS Switch 1</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
@@ -11011,17 +11095,17 @@
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>OS W-1</t>
+          <t>Track W-1</t>
         </is>
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>OS 1</t>
+          <t>OS Switch 1</t>
         </is>
       </c>
       <c r="H3" s="3" t="inlineStr">
         <is>
-          <t>OS 3+W-1</t>
+          <t>OS Switch 3+W-1</t>
         </is>
       </c>
       <c r="I3" s="3" t="inlineStr">
@@ -11092,7 +11176,7 @@
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>OS 1</t>
+          <t>OS Switch 1</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
@@ -11102,17 +11186,17 @@
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>OS W-1</t>
+          <t>Track W-1</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>OS 1</t>
+          <t>OS Switch 1</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>OS 3+W-1</t>
+          <t>OS Switch 3+W-1</t>
         </is>
       </c>
       <c r="I4" s="3" t="inlineStr">
@@ -11183,7 +11267,7 @@
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>OS 1</t>
+          <t>OS Switch 1</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
@@ -11193,17 +11277,17 @@
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>OS W-2</t>
+          <t>Track W-2</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>OS 1</t>
+          <t>OS Switch 1</t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>OS 3+W-2</t>
+          <t>OS Switch 3+W-2</t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr">
@@ -11270,7 +11354,7 @@
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>OS 1</t>
+          <t>OS Switch 1</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
@@ -11280,17 +11364,17 @@
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>OS W-2</t>
+          <t>Track W-2</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>OS 1</t>
+          <t>OS Switch 1</t>
         </is>
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
-          <t>OS 3+W-2</t>
+          <t>OS Switch 3+W-2</t>
         </is>
       </c>
       <c r="I6" s="3" t="inlineStr">
@@ -11361,7 +11445,7 @@
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>OS 1</t>
+          <t>OS Switch 1</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
@@ -11371,17 +11455,17 @@
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>OS W-2</t>
+          <t>Track W-2</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>OS 1</t>
+          <t>OS Switch 1</t>
         </is>
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t>OS 3+W-2</t>
+          <t>OS Switch 3+W-2</t>
         </is>
       </c>
       <c r="I7" s="3" t="inlineStr">
@@ -11452,7 +11536,7 @@
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>OS 1</t>
+          <t>OS Switch 1</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
@@ -11467,12 +11551,12 @@
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>OS 1</t>
+          <t>OS Switch 1</t>
         </is>
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t>OS Brick-Plane + OS 102</t>
+          <t>Track Brick-Plane + OS 102</t>
         </is>
       </c>
       <c r="I8" s="3" t="inlineStr">
@@ -11535,7 +11619,7 @@
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>OS 1</t>
+          <t>OS Switch 1</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
@@ -11550,12 +11634,12 @@
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>OS 1</t>
+          <t>OS Switch 1</t>
         </is>
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t>OS Brick-Plane + OS 102</t>
+          <t>Track Brick-Plane + OS 102</t>
         </is>
       </c>
       <c r="I9" s="3" t="inlineStr">
@@ -11622,7 +11706,7 @@
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>OS 1</t>
+          <t>OS Switch 1</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
@@ -11637,12 +11721,12 @@
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>OS 1</t>
+          <t>OS Switch 1</t>
         </is>
       </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
-          <t>OS Brick-Plane + OS 102</t>
+          <t>Track Brick-Plane + OS 102</t>
         </is>
       </c>
       <c r="I10" s="3" t="inlineStr">
@@ -11709,12 +11793,12 @@
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>OS 3</t>
+          <t>OS Switch 3</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>OS W-1</t>
+          <t>Track W-1</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
@@ -11724,12 +11808,12 @@
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>OS 3</t>
+          <t>OS Switch 3</t>
         </is>
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t>OS 1</t>
+          <t>OS Switch 1</t>
         </is>
       </c>
       <c r="I11" s="3" t="inlineStr">
@@ -11796,12 +11880,12 @@
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>OS 3</t>
+          <t>OS Switch 3</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>OS W-1</t>
+          <t>Track W-1</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
@@ -11811,12 +11895,12 @@
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>OS 3</t>
+          <t>OS Switch 3</t>
         </is>
       </c>
       <c r="H12" s="3" t="inlineStr">
         <is>
-          <t>OS 1</t>
+          <t>OS Switch 1</t>
         </is>
       </c>
       <c r="I12" s="3" t="inlineStr">
@@ -11887,12 +11971,12 @@
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>OS 3</t>
+          <t>OS Switch 3</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>OS W-1</t>
+          <t>Track W-1</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
@@ -11902,12 +11986,12 @@
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>OS 3</t>
+          <t>OS Switch 3</t>
         </is>
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t>OS 1</t>
+          <t>OS Switch 1</t>
         </is>
       </c>
       <c r="I13" s="3" t="inlineStr">
@@ -11978,12 +12062,12 @@
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>OS 3</t>
+          <t>OS Switch 3</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>OS W-2</t>
+          <t>Track W-2</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
@@ -11993,12 +12077,12 @@
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>OS 3</t>
+          <t>OS Switch 3</t>
         </is>
       </c>
       <c r="H14" s="3" t="inlineStr">
         <is>
-          <t>OS 1</t>
+          <t>OS Switch 1</t>
         </is>
       </c>
       <c r="I14" s="3" t="inlineStr">
@@ -12065,12 +12149,12 @@
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>OS 3</t>
+          <t>OS Switch 3</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>OS W-2</t>
+          <t>Track W-2</t>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
@@ -12080,12 +12164,12 @@
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>OS 3</t>
+          <t>OS Switch 3</t>
         </is>
       </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
-          <t>OS 1</t>
+          <t>OS Switch 1</t>
         </is>
       </c>
       <c r="I15" s="3" t="inlineStr">
@@ -12156,12 +12240,12 @@
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>OS 3</t>
+          <t>OS Switch 3</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>OS W-2</t>
+          <t>Track W-2</t>
         </is>
       </c>
       <c r="F16" s="3" t="inlineStr">
@@ -12171,12 +12255,12 @@
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>OS 3</t>
+          <t>OS Switch 3</t>
         </is>
       </c>
       <c r="H16" s="3" t="inlineStr">
         <is>
-          <t>OS 1</t>
+          <t>OS Switch 1</t>
         </is>
       </c>
       <c r="I16" s="3" t="inlineStr">
@@ -12247,12 +12331,12 @@
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>OS W-1</t>
+          <t>Track W-1</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>OS W-1</t>
+          <t>Track W-1</t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
@@ -12262,7 +12346,7 @@
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>OS W-1</t>
+          <t>Track W-1</t>
         </is>
       </c>
       <c r="H17" s="3" t="inlineStr"/>
@@ -12322,12 +12406,12 @@
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>OS W-2</t>
+          <t>Track W-2</t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>OS W-2</t>
+          <t>Track W-2</t>
         </is>
       </c>
       <c r="F18" s="3" t="inlineStr">
@@ -12337,7 +12421,7 @@
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>OS W-2</t>
+          <t>Track W-2</t>
         </is>
       </c>
       <c r="H18" s="3" t="inlineStr"/>
@@ -12397,12 +12481,12 @@
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>OS 5</t>
+          <t>OS Switch 5</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>OS Scale / Brick shaft</t>
+          <t>Track Scale / Brick shaft</t>
         </is>
       </c>
       <c r="F19" s="3" t="inlineStr">
@@ -12412,12 +12496,12 @@
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>OS 5</t>
+          <t>OS Switch 5</t>
         </is>
       </c>
       <c r="H19" s="3" t="inlineStr">
         <is>
-          <t>OS Scale or East Main path</t>
+          <t>Track Scale or East Main path</t>
         </is>
       </c>
       <c r="I19" s="3" t="inlineStr">
@@ -12458,7 +12542,7 @@
       </c>
       <c r="Y19" s="3" t="inlineStr">
         <is>
-          <t>Eastbound on OS Scale / main side of Plane. Adjust N/R if field frog is opposite.</t>
+          <t>Eastbound on Track Scale / main side of Plane. Adjust N/R if field frog is opposite.</t>
         </is>
       </c>
     </row>
@@ -12480,12 +12564,12 @@
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>OS 5</t>
+          <t>OS Switch 5</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>OS Scale / Brick shaft</t>
+          <t>Track Scale / Brick shaft</t>
         </is>
       </c>
       <c r="F20" s="3" t="inlineStr">
@@ -12495,12 +12579,12 @@
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>OS 5</t>
+          <t>OS Switch 5</t>
         </is>
       </c>
       <c r="H20" s="3" t="inlineStr">
         <is>
-          <t>OS Scale or East Main path</t>
+          <t>Track Scale or East Main path</t>
         </is>
       </c>
       <c r="I20" s="3" t="inlineStr">
@@ -12545,7 +12629,7 @@
       </c>
       <c r="Y20" s="3" t="inlineStr">
         <is>
-          <t>Eastbound on OS Scale / main side of Plane. Adjust N/R if field frog is opposite.</t>
+          <t>Eastbound on Track Scale / main side of Plane. Adjust N/R if field frog is opposite.</t>
         </is>
       </c>
     </row>
@@ -12567,12 +12651,12 @@
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>OS 5</t>
+          <t>OS Switch 5</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>OS Scale / Brick shaft</t>
+          <t>Track Scale / Brick shaft</t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr">
@@ -12582,12 +12666,12 @@
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>OS 5</t>
+          <t>OS Switch 5</t>
         </is>
       </c>
       <c r="H21" s="3" t="inlineStr">
         <is>
-          <t>OS Scale or East Main path</t>
+          <t>Track Scale or East Main path</t>
         </is>
       </c>
       <c r="I21" s="3" t="inlineStr">
@@ -12632,7 +12716,7 @@
       </c>
       <c r="Y21" s="3" t="inlineStr">
         <is>
-          <t>Eastbound on OS Scale / main side of Plane. Adjust N/R if field frog is opposite.</t>
+          <t>Eastbound on Track Scale / main side of Plane. Adjust N/R if field frog is opposite.</t>
         </is>
       </c>
     </row>
@@ -12654,7 +12738,7 @@
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>OS 5</t>
+          <t>OS Switch 5</t>
         </is>
       </c>
       <c r="E22" s="3" t="inlineStr">
@@ -12669,7 +12753,7 @@
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>OS 5</t>
+          <t>OS Switch 5</t>
         </is>
       </c>
       <c r="H22" s="3" t="inlineStr">
@@ -12737,7 +12821,7 @@
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>OS 5</t>
+          <t>OS Switch 5</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
@@ -12752,7 +12836,7 @@
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>OS 5</t>
+          <t>OS Switch 5</t>
         </is>
       </c>
       <c r="H23" s="3" t="inlineStr">
@@ -12824,7 +12908,7 @@
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>OS 5</t>
+          <t>OS Switch 5</t>
         </is>
       </c>
       <c r="E24" s="3" t="inlineStr">
@@ -12839,7 +12923,7 @@
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>OS 5</t>
+          <t>OS Switch 5</t>
         </is>
       </c>
       <c r="H24" s="3" t="inlineStr">
@@ -12911,27 +12995,27 @@
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>OS 7</t>
+          <t>OS Switch 7</t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>OS Scale / Plane</t>
+          <t>Track Scale / Plane</t>
         </is>
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t>OS Barn / east</t>
+          <t>Track Barn / east</t>
         </is>
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>OS 7</t>
+          <t>OS Switch 7</t>
         </is>
       </c>
       <c r="H25" s="3" t="inlineStr">
         <is>
-          <t>OS Barn</t>
+          <t>Track Barn</t>
         </is>
       </c>
       <c r="I25" s="3" t="inlineStr">
@@ -12994,27 +13078,27 @@
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t>OS 7</t>
+          <t>OS Switch 7</t>
         </is>
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t>OS Scale / Plane</t>
+          <t>Track Scale / Plane</t>
         </is>
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
-          <t>OS Barn / east</t>
+          <t>Track Barn / east</t>
         </is>
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>OS 7</t>
+          <t>OS Switch 7</t>
         </is>
       </c>
       <c r="H26" s="3" t="inlineStr">
         <is>
-          <t>OS Barn</t>
+          <t>Track Barn</t>
         </is>
       </c>
       <c r="I26" s="3" t="inlineStr">
@@ -13081,27 +13165,27 @@
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>OS 7</t>
+          <t>OS Switch 7</t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t>OS Scale / Plane</t>
+          <t>Track Scale / Plane</t>
         </is>
       </c>
       <c r="F27" s="3" t="inlineStr">
         <is>
-          <t>OS Barn / east</t>
+          <t>Track Barn / east</t>
         </is>
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>OS 7</t>
+          <t>OS Switch 7</t>
         </is>
       </c>
       <c r="H27" s="3" t="inlineStr">
         <is>
-          <t>OS Barn</t>
+          <t>Track Barn</t>
         </is>
       </c>
       <c r="I27" s="3" t="inlineStr">
@@ -13168,12 +13252,12 @@
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>OS 7</t>
+          <t>OS Switch 7</t>
         </is>
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t>OS Barn</t>
+          <t>Track Barn</t>
         </is>
       </c>
       <c r="F28" s="3" t="inlineStr">
@@ -13183,12 +13267,12 @@
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>OS 7</t>
+          <t>OS Switch 7</t>
         </is>
       </c>
       <c r="H28" s="3" t="inlineStr">
         <is>
-          <t>OS Scale</t>
+          <t>Track Scale</t>
         </is>
       </c>
       <c r="I28" s="3" t="inlineStr">
@@ -13251,12 +13335,12 @@
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>OS 7</t>
+          <t>OS Switch 7</t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t>OS Barn</t>
+          <t>Track Barn</t>
         </is>
       </c>
       <c r="F29" s="3" t="inlineStr">
@@ -13266,12 +13350,12 @@
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>OS 7</t>
+          <t>OS Switch 7</t>
         </is>
       </c>
       <c r="H29" s="3" t="inlineStr">
         <is>
-          <t>OS Scale</t>
+          <t>Track Scale</t>
         </is>
       </c>
       <c r="I29" s="3" t="inlineStr">
@@ -13338,12 +13422,12 @@
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>OS 7</t>
+          <t>OS Switch 7</t>
         </is>
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t>OS Barn</t>
+          <t>Track Barn</t>
         </is>
       </c>
       <c r="F30" s="3" t="inlineStr">
@@ -13353,12 +13437,12 @@
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>OS 7</t>
+          <t>OS Switch 7</t>
         </is>
       </c>
       <c r="H30" s="3" t="inlineStr">
         <is>
-          <t>OS Scale</t>
+          <t>Track Scale</t>
         </is>
       </c>
       <c r="I30" s="3" t="inlineStr">
@@ -13425,7 +13509,7 @@
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>OS 7b</t>
+          <t>OS Switch 7b</t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
@@ -13440,7 +13524,7 @@
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>OS 7b</t>
+          <t>OS Switch 7b</t>
         </is>
       </c>
       <c r="H31" s="3" t="inlineStr">
@@ -13508,7 +13592,7 @@
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>OS 7b</t>
+          <t>OS Switch 7b</t>
         </is>
       </c>
       <c r="E32" s="3" t="inlineStr">
@@ -13523,7 +13607,7 @@
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t>OS 7b</t>
+          <t>OS Switch 7b</t>
         </is>
       </c>
       <c r="H32" s="3" t="inlineStr">
@@ -13595,7 +13679,7 @@
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>OS 7b</t>
+          <t>OS Switch 7b</t>
         </is>
       </c>
       <c r="E33" s="3" t="inlineStr">
@@ -13610,7 +13694,7 @@
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t>OS 7b</t>
+          <t>OS Switch 7b</t>
         </is>
       </c>
       <c r="H33" s="3" t="inlineStr">
@@ -13682,7 +13766,7 @@
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t>OS 7b</t>
+          <t>OS Switch 7b</t>
         </is>
       </c>
       <c r="E34" s="3" t="inlineStr">
@@ -13697,7 +13781,7 @@
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t>OS 7b</t>
+          <t>OS Switch 7b</t>
         </is>
       </c>
       <c r="H34" s="3" t="inlineStr">
@@ -13765,7 +13849,7 @@
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t>OS 7b</t>
+          <t>OS Switch 7b</t>
         </is>
       </c>
       <c r="E35" s="3" t="inlineStr">
@@ -13780,7 +13864,7 @@
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t>OS 7b</t>
+          <t>OS Switch 7b</t>
         </is>
       </c>
       <c r="H35" s="3" t="inlineStr">
@@ -13852,7 +13936,7 @@
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t>OS 7b</t>
+          <t>OS Switch 7b</t>
         </is>
       </c>
       <c r="E36" s="3" t="inlineStr">
@@ -13867,7 +13951,7 @@
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t>OS 7b</t>
+          <t>OS Switch 7b</t>
         </is>
       </c>
       <c r="H36" s="3" t="inlineStr">
@@ -13939,7 +14023,7 @@
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t>OS 23a</t>
+          <t>OS Switch 23a</t>
         </is>
       </c>
       <c r="E37" s="3" t="inlineStr">
@@ -13954,7 +14038,7 @@
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t>OS 23a</t>
+          <t>OS Switch 23a</t>
         </is>
       </c>
       <c r="H37" s="3" t="inlineStr">
@@ -14022,7 +14106,7 @@
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t>OS 23a</t>
+          <t>OS Switch 23a</t>
         </is>
       </c>
       <c r="E38" s="3" t="inlineStr">
@@ -14037,7 +14121,7 @@
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t>OS 23a</t>
+          <t>OS Switch 23a</t>
         </is>
       </c>
       <c r="H38" s="3" t="inlineStr">
@@ -14109,7 +14193,7 @@
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t>OS 23a</t>
+          <t>OS Switch 23a</t>
         </is>
       </c>
       <c r="E39" s="3" t="inlineStr">
@@ -14124,7 +14208,7 @@
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t>OS 23a</t>
+          <t>OS Switch 23a</t>
         </is>
       </c>
       <c r="H39" s="3" t="inlineStr">
@@ -14196,7 +14280,7 @@
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t>OS 23a</t>
+          <t>OS Switch 23a</t>
         </is>
       </c>
       <c r="E40" s="3" t="inlineStr">
@@ -14211,7 +14295,7 @@
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t>OS 23a</t>
+          <t>OS Switch 23a</t>
         </is>
       </c>
       <c r="H40" s="3" t="inlineStr">
@@ -14279,7 +14363,7 @@
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t>OS 23a</t>
+          <t>OS Switch 23a</t>
         </is>
       </c>
       <c r="E41" s="3" t="inlineStr">
@@ -14294,7 +14378,7 @@
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t>OS 23a</t>
+          <t>OS Switch 23a</t>
         </is>
       </c>
       <c r="H41" s="3" t="inlineStr">
@@ -14366,7 +14450,7 @@
       </c>
       <c r="D42" s="3" t="inlineStr">
         <is>
-          <t>OS 23a</t>
+          <t>OS Switch 23a</t>
         </is>
       </c>
       <c r="E42" s="3" t="inlineStr">
@@ -14381,7 +14465,7 @@
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t>OS 23a</t>
+          <t>OS Switch 23a</t>
         </is>
       </c>
       <c r="H42" s="3" t="inlineStr">
@@ -14453,12 +14537,12 @@
       </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
-          <t>OS 23b</t>
+          <t>OS Switch 23b</t>
         </is>
       </c>
       <c r="E43" s="3" t="inlineStr">
         <is>
-          <t>OS S-R</t>
+          <t>Track S-R</t>
         </is>
       </c>
       <c r="F43" s="3" t="inlineStr">
@@ -14468,7 +14552,7 @@
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t>OS 23b</t>
+          <t>OS Switch 23b</t>
         </is>
       </c>
       <c r="H43" s="3" t="inlineStr">
@@ -14536,12 +14620,12 @@
       </c>
       <c r="D44" s="3" t="inlineStr">
         <is>
-          <t>OS 23b</t>
+          <t>OS Switch 23b</t>
         </is>
       </c>
       <c r="E44" s="3" t="inlineStr">
         <is>
-          <t>OS S-R</t>
+          <t>Track S-R</t>
         </is>
       </c>
       <c r="F44" s="3" t="inlineStr">
@@ -14551,7 +14635,7 @@
       </c>
       <c r="G44" s="3" t="inlineStr">
         <is>
-          <t>OS 23b</t>
+          <t>OS Switch 23b</t>
         </is>
       </c>
       <c r="H44" s="3" t="inlineStr">
@@ -14623,12 +14707,12 @@
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t>OS 23b</t>
+          <t>OS Switch 23b</t>
         </is>
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
-          <t>OS S-R</t>
+          <t>Track S-R</t>
         </is>
       </c>
       <c r="F45" s="3" t="inlineStr">
@@ -14638,7 +14722,7 @@
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t>OS 23b</t>
+          <t>OS Switch 23b</t>
         </is>
       </c>
       <c r="H45" s="3" t="inlineStr">
@@ -14710,7 +14794,7 @@
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t>OS 33</t>
+          <t>OS Switch 33</t>
         </is>
       </c>
       <c r="E46" s="3" t="inlineStr">
@@ -14725,7 +14809,7 @@
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t>OS 33</t>
+          <t>OS Switch 33</t>
         </is>
       </c>
       <c r="H46" s="3" t="inlineStr">
@@ -14793,7 +14877,7 @@
       </c>
       <c r="D47" s="3" t="inlineStr">
         <is>
-          <t>OS 33</t>
+          <t>OS Switch 33</t>
         </is>
       </c>
       <c r="E47" s="3" t="inlineStr">
@@ -14808,7 +14892,7 @@
       </c>
       <c r="G47" s="3" t="inlineStr">
         <is>
-          <t>OS 33</t>
+          <t>OS Switch 33</t>
         </is>
       </c>
       <c r="H47" s="3" t="inlineStr">
@@ -14880,7 +14964,7 @@
       </c>
       <c r="D48" s="3" t="inlineStr">
         <is>
-          <t>OS 33</t>
+          <t>OS Switch 33</t>
         </is>
       </c>
       <c r="E48" s="3" t="inlineStr">
@@ -14895,7 +14979,7 @@
       </c>
       <c r="G48" s="3" t="inlineStr">
         <is>
-          <t>OS 33</t>
+          <t>OS Switch 33</t>
         </is>
       </c>
       <c r="H48" s="3" t="inlineStr">
@@ -14967,7 +15051,7 @@
       </c>
       <c r="D49" s="3" t="inlineStr">
         <is>
-          <t>OS 31</t>
+          <t>OS Switch 31</t>
         </is>
       </c>
       <c r="E49" s="3" t="inlineStr">
@@ -14982,7 +15066,7 @@
       </c>
       <c r="G49" s="3" t="inlineStr">
         <is>
-          <t>OS 31</t>
+          <t>OS Switch 31</t>
         </is>
       </c>
       <c r="H49" s="3" t="inlineStr">
@@ -15050,7 +15134,7 @@
       </c>
       <c r="D50" s="3" t="inlineStr">
         <is>
-          <t>OS 31</t>
+          <t>OS Switch 31</t>
         </is>
       </c>
       <c r="E50" s="3" t="inlineStr">
@@ -15065,7 +15149,7 @@
       </c>
       <c r="G50" s="3" t="inlineStr">
         <is>
-          <t>OS 31</t>
+          <t>OS Switch 31</t>
         </is>
       </c>
       <c r="H50" s="3" t="inlineStr">
@@ -15137,7 +15221,7 @@
       </c>
       <c r="D51" s="3" t="inlineStr">
         <is>
-          <t>OS 31</t>
+          <t>OS Switch 31</t>
         </is>
       </c>
       <c r="E51" s="3" t="inlineStr">
@@ -15152,7 +15236,7 @@
       </c>
       <c r="G51" s="3" t="inlineStr">
         <is>
-          <t>OS 31</t>
+          <t>OS Switch 31</t>
         </is>
       </c>
       <c r="H51" s="3" t="inlineStr">
@@ -15224,7 +15308,7 @@
       </c>
       <c r="D52" s="3" t="inlineStr">
         <is>
-          <t>OS 33</t>
+          <t>OS Switch 33</t>
         </is>
       </c>
       <c r="E52" s="3" t="inlineStr">
@@ -15239,7 +15323,7 @@
       </c>
       <c r="G52" s="3" t="inlineStr">
         <is>
-          <t>OS 33</t>
+          <t>OS Switch 33</t>
         </is>
       </c>
       <c r="H52" s="3" t="inlineStr">
@@ -15307,7 +15391,7 @@
       </c>
       <c r="D53" s="3" t="inlineStr">
         <is>
-          <t>OS 33</t>
+          <t>OS Switch 33</t>
         </is>
       </c>
       <c r="E53" s="3" t="inlineStr">
@@ -15322,7 +15406,7 @@
       </c>
       <c r="G53" s="3" t="inlineStr">
         <is>
-          <t>OS 33</t>
+          <t>OS Switch 33</t>
         </is>
       </c>
       <c r="H53" s="3" t="inlineStr">
@@ -15394,7 +15478,7 @@
       </c>
       <c r="D54" s="3" t="inlineStr">
         <is>
-          <t>OS 33</t>
+          <t>OS Switch 33</t>
         </is>
       </c>
       <c r="E54" s="3" t="inlineStr">
@@ -15409,7 +15493,7 @@
       </c>
       <c r="G54" s="3" t="inlineStr">
         <is>
-          <t>OS 33</t>
+          <t>OS Switch 33</t>
         </is>
       </c>
       <c r="H54" s="3" t="inlineStr">
@@ -15481,7 +15565,7 @@
       </c>
       <c r="D55" s="3" t="inlineStr">
         <is>
-          <t>OS 35b</t>
+          <t>OS Switch 35b</t>
         </is>
       </c>
       <c r="E55" s="3" t="inlineStr">
@@ -15496,12 +15580,12 @@
       </c>
       <c r="G55" s="3" t="inlineStr">
         <is>
-          <t>OS 35b</t>
+          <t>OS Switch 35b</t>
         </is>
       </c>
       <c r="H55" s="3" t="inlineStr">
         <is>
-          <t>OS 39</t>
+          <t>OS Switch 39</t>
         </is>
       </c>
       <c r="I55" s="3" t="inlineStr">
@@ -15564,7 +15648,7 @@
       </c>
       <c r="D56" s="3" t="inlineStr">
         <is>
-          <t>OS 35b</t>
+          <t>OS Switch 35b</t>
         </is>
       </c>
       <c r="E56" s="3" t="inlineStr">
@@ -15579,12 +15663,12 @@
       </c>
       <c r="G56" s="3" t="inlineStr">
         <is>
-          <t>OS 35b</t>
+          <t>OS Switch 35b</t>
         </is>
       </c>
       <c r="H56" s="3" t="inlineStr">
         <is>
-          <t>OS 39</t>
+          <t>OS Switch 39</t>
         </is>
       </c>
       <c r="I56" s="3" t="inlineStr">
@@ -15651,7 +15735,7 @@
       </c>
       <c r="D57" s="3" t="inlineStr">
         <is>
-          <t>OS 35b</t>
+          <t>OS Switch 35b</t>
         </is>
       </c>
       <c r="E57" s="3" t="inlineStr">
@@ -15666,12 +15750,12 @@
       </c>
       <c r="G57" s="3" t="inlineStr">
         <is>
-          <t>OS 35b</t>
+          <t>OS Switch 35b</t>
         </is>
       </c>
       <c r="H57" s="3" t="inlineStr">
         <is>
-          <t>OS 39</t>
+          <t>OS Switch 39</t>
         </is>
       </c>
       <c r="I57" s="3" t="inlineStr">
@@ -15738,7 +15822,7 @@
       </c>
       <c r="D58" s="3" t="inlineStr">
         <is>
-          <t>OS 35a</t>
+          <t>OS Switch 35a</t>
         </is>
       </c>
       <c r="E58" s="3" t="inlineStr">
@@ -15753,12 +15837,12 @@
       </c>
       <c r="G58" s="3" t="inlineStr">
         <is>
-          <t>OS 35a</t>
+          <t>OS Switch 35a</t>
         </is>
       </c>
       <c r="H58" s="3" t="inlineStr">
         <is>
-          <t>OS 37</t>
+          <t>OS Switch 37</t>
         </is>
       </c>
       <c r="I58" s="3" t="inlineStr">
@@ -15821,7 +15905,7 @@
       </c>
       <c r="D59" s="3" t="inlineStr">
         <is>
-          <t>OS 35a</t>
+          <t>OS Switch 35a</t>
         </is>
       </c>
       <c r="E59" s="3" t="inlineStr">
@@ -15836,12 +15920,12 @@
       </c>
       <c r="G59" s="3" t="inlineStr">
         <is>
-          <t>OS 35a</t>
+          <t>OS Switch 35a</t>
         </is>
       </c>
       <c r="H59" s="3" t="inlineStr">
         <is>
-          <t>OS 37</t>
+          <t>OS Switch 37</t>
         </is>
       </c>
       <c r="I59" s="3" t="inlineStr">
@@ -15908,7 +15992,7 @@
       </c>
       <c r="D60" s="3" t="inlineStr">
         <is>
-          <t>OS 35a</t>
+          <t>OS Switch 35a</t>
         </is>
       </c>
       <c r="E60" s="3" t="inlineStr">
@@ -15923,12 +16007,12 @@
       </c>
       <c r="G60" s="3" t="inlineStr">
         <is>
-          <t>OS 35a</t>
+          <t>OS Switch 35a</t>
         </is>
       </c>
       <c r="H60" s="3" t="inlineStr">
         <is>
-          <t>OS 37</t>
+          <t>OS Switch 37</t>
         </is>
       </c>
       <c r="I60" s="3" t="inlineStr">
@@ -15995,7 +16079,7 @@
       </c>
       <c r="D61" s="3" t="inlineStr">
         <is>
-          <t>OS 39</t>
+          <t>OS Switch 39</t>
         </is>
       </c>
       <c r="E61" s="3" t="inlineStr">
@@ -16010,7 +16094,7 @@
       </c>
       <c r="G61" s="3" t="inlineStr">
         <is>
-          <t>OS 39</t>
+          <t>OS Switch 39</t>
         </is>
       </c>
       <c r="H61" s="3" t="inlineStr">
@@ -16078,7 +16162,7 @@
       </c>
       <c r="D62" s="3" t="inlineStr">
         <is>
-          <t>OS 39</t>
+          <t>OS Switch 39</t>
         </is>
       </c>
       <c r="E62" s="3" t="inlineStr">
@@ -16093,7 +16177,7 @@
       </c>
       <c r="G62" s="3" t="inlineStr">
         <is>
-          <t>OS 39</t>
+          <t>OS Switch 39</t>
         </is>
       </c>
       <c r="H62" s="3" t="inlineStr">
@@ -16165,7 +16249,7 @@
       </c>
       <c r="D63" s="3" t="inlineStr">
         <is>
-          <t>OS 39</t>
+          <t>OS Switch 39</t>
         </is>
       </c>
       <c r="E63" s="3" t="inlineStr">
@@ -16180,7 +16264,7 @@
       </c>
       <c r="G63" s="3" t="inlineStr">
         <is>
-          <t>OS 39</t>
+          <t>OS Switch 39</t>
         </is>
       </c>
       <c r="H63" s="3" t="inlineStr">
@@ -16252,7 +16336,7 @@
       </c>
       <c r="D64" s="3" t="inlineStr">
         <is>
-          <t>OS 37</t>
+          <t>OS Switch 37</t>
         </is>
       </c>
       <c r="E64" s="3" t="inlineStr">
@@ -16267,7 +16351,7 @@
       </c>
       <c r="G64" s="3" t="inlineStr">
         <is>
-          <t>OS 37</t>
+          <t>OS Switch 37</t>
         </is>
       </c>
       <c r="H64" s="3" t="inlineStr">
@@ -16335,7 +16419,7 @@
       </c>
       <c r="D65" s="3" t="inlineStr">
         <is>
-          <t>OS 37</t>
+          <t>OS Switch 37</t>
         </is>
       </c>
       <c r="E65" s="3" t="inlineStr">
@@ -16350,7 +16434,7 @@
       </c>
       <c r="G65" s="3" t="inlineStr">
         <is>
-          <t>OS 37</t>
+          <t>OS Switch 37</t>
         </is>
       </c>
       <c r="H65" s="3" t="inlineStr">
@@ -16422,7 +16506,7 @@
       </c>
       <c r="D66" s="3" t="inlineStr">
         <is>
-          <t>OS 37</t>
+          <t>OS Switch 37</t>
         </is>
       </c>
       <c r="E66" s="3" t="inlineStr">
@@ -16437,7 +16521,7 @@
       </c>
       <c r="G66" s="3" t="inlineStr">
         <is>
-          <t>OS 37</t>
+          <t>OS Switch 37</t>
         </is>
       </c>
       <c r="H66" s="3" t="inlineStr">
@@ -16509,27 +16593,27 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>OS K-1</t>
+          <t>Track K-1</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>OS K-1</t>
+          <t>Track K-1</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>OS West Main Ext</t>
+          <t>Track West Main Ext</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>OS 39</t>
+          <t>OS Switch 39</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>OS West Main Ext</t>
+          <t>Track West Main Ext</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -16586,27 +16670,27 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>OS K-1</t>
+          <t>Track K-1</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>OS K-1</t>
+          <t>Track K-1</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>OS West Main Ext</t>
+          <t>Track West Main Ext</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>OS 39</t>
+          <t>OS Switch 39</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>OS West Main Ext</t>
+          <t>Track West Main Ext</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -16668,27 +16752,27 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>OS K-1</t>
+          <t>Track K-1</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>OS K-1</t>
+          <t>Track K-1</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>OS West Main Ext</t>
+          <t>Track West Main Ext</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>OS 39</t>
+          <t>OS Switch 39</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>OS West Main Ext</t>
+          <t>Track West Main Ext</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -16750,27 +16834,27 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>OS K-1</t>
+          <t>Track K-1</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>OS K-1</t>
+          <t>Track K-1</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>OS East Lead</t>
+          <t>Track East Lead</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>OS 39</t>
+          <t>OS Switch 39</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>OS East Lead</t>
+          <t>Track East Lead</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -16827,27 +16911,27 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>OS K-1</t>
+          <t>Track K-1</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>OS K-1</t>
+          <t>Track K-1</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>OS East Lead</t>
+          <t>Track East Lead</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>OS 39</t>
+          <t>OS Switch 39</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>OS East Lead</t>
+          <t>Track East Lead</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -16909,27 +16993,27 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>OS K-1</t>
+          <t>Track K-1</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>OS K-1</t>
+          <t>Track K-1</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>OS East Lead</t>
+          <t>Track East Lead</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>OS 39</t>
+          <t>OS Switch 39</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>OS East Lead</t>
+          <t>Track East Lead</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -16991,27 +17075,27 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>OS K-2</t>
+          <t>Track K-2</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>OS K-2</t>
+          <t>Track K-2</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>OS West Main Ext</t>
+          <t>Track West Main Ext</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>OS 37</t>
+          <t>OS Switch 37</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>OS West Main Ext</t>
+          <t>Track West Main Ext</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -17068,27 +17152,27 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>OS K-2</t>
+          <t>Track K-2</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>OS K-2</t>
+          <t>Track K-2</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>OS West Main Ext</t>
+          <t>Track West Main Ext</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>OS 37</t>
+          <t>OS Switch 37</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>OS West Main Ext</t>
+          <t>Track West Main Ext</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -17150,27 +17234,27 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>OS K-2</t>
+          <t>Track K-2</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>OS K-2</t>
+          <t>Track K-2</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>OS West Main Ext</t>
+          <t>Track West Main Ext</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>OS 37</t>
+          <t>OS Switch 37</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>OS West Main Ext</t>
+          <t>Track West Main Ext</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -17232,27 +17316,27 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>OS K-2</t>
+          <t>Track K-2</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>OS K-2</t>
+          <t>Track K-2</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>OS East Lead</t>
+          <t>Track East Lead</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>OS 37</t>
+          <t>OS Switch 37</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>OS East Lead</t>
+          <t>Track East Lead</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -17309,27 +17393,27 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>OS K-2</t>
+          <t>Track K-2</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>OS K-2</t>
+          <t>Track K-2</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>OS East Lead</t>
+          <t>Track East Lead</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>OS 37</t>
+          <t>OS Switch 37</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>OS East Lead</t>
+          <t>Track East Lead</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -17391,27 +17475,27 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>OS K-2</t>
+          <t>Track K-2</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>OS K-2</t>
+          <t>Track K-2</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>OS East Lead</t>
+          <t>Track East Lead</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>OS 37</t>
+          <t>OS Switch 37</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>OS East Lead</t>
+          <t>Track East Lead</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -17473,27 +17557,27 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>OS McKees Rocks</t>
+          <t>Track McKees Rocks</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>OS McKeesport</t>
+          <t>Track McKeesport</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>OS McKees Rocks</t>
+          <t>Track McKees Rocks</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>OS McKees Rocks</t>
+          <t>Track McKees Rocks</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>OS 39</t>
+          <t>OS Switch 39</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -17545,27 +17629,27 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>OS McKees Rocks</t>
+          <t>Track McKees Rocks</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>OS McKeesport</t>
+          <t>Track McKeesport</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>OS McKees Rocks</t>
+          <t>Track McKees Rocks</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>OS McKees Rocks</t>
+          <t>Track McKees Rocks</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>OS 39</t>
+          <t>OS Switch 39</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -17622,27 +17706,27 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>OS McKees Rocks</t>
+          <t>Track McKees Rocks</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>OS McKeesport</t>
+          <t>Track McKeesport</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>OS McKees Rocks</t>
+          <t>Track McKees Rocks</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>OS McKees Rocks</t>
+          <t>Track McKees Rocks</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>OS 39</t>
+          <t>OS Switch 39</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -17699,27 +17783,27 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>OS McKeesport</t>
+          <t>Track McKeesport</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>OS McKees Rocks</t>
+          <t>Track McKees Rocks</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>OS McKeesport</t>
+          <t>Track McKeesport</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>OS McKeesport</t>
+          <t>Track McKeesport</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>OS 37</t>
+          <t>OS Switch 37</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
@@ -17771,27 +17855,27 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>OS McKeesport</t>
+          <t>Track McKeesport</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>OS McKees Rocks</t>
+          <t>Track McKees Rocks</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>OS McKeesport</t>
+          <t>Track McKeesport</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>OS McKeesport</t>
+          <t>Track McKeesport</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>OS 37</t>
+          <t>OS Switch 37</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -17848,27 +17932,27 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>OS McKeesport</t>
+          <t>Track McKeesport</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>OS McKees Rocks</t>
+          <t>Track McKees Rocks</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>OS McKeesport</t>
+          <t>Track McKeesport</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>OS McKeesport</t>
+          <t>Track McKeesport</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>OS 37</t>
+          <t>OS Switch 37</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -17969,7 +18053,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>OS McKees Rocks</t>
+          <t>McKees Rocks</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
@@ -17984,7 +18068,7 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>OS McKees Rocks</t>
+          <t>McKees Rocks</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
@@ -18001,7 +18085,7 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>OS McKeesport</t>
+          <t>McKeesport</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
@@ -18016,7 +18100,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>OS McKeesport</t>
+          <t>McKeesport</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
@@ -18033,7 +18117,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>OS 37</t>
+          <t>OS Switch 37</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
@@ -18048,7 +18132,7 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>OS 37</t>
+          <t>OS Switch 37</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
@@ -18065,7 +18149,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>OS 39</t>
+          <t>OS Switch 39</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
@@ -18080,7 +18164,7 @@
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>OS 39</t>
+          <t>OS Switch 39</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
@@ -18097,7 +18181,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>OS 35b</t>
+          <t>OS Switch 35b</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
@@ -18112,7 +18196,7 @@
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>OS 35b</t>
+          <t>OS Switch 35b</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
@@ -18129,7 +18213,7 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>OS 35a</t>
+          <t>OS Switch 35a</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
@@ -18144,7 +18228,7 @@
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>OS 35a</t>
+          <t>OS Switch 35a</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
@@ -18161,7 +18245,7 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>OS East Lead</t>
+          <t>East Lead</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
@@ -18176,7 +18260,7 @@
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>OS East Lead</t>
+          <t>East Lead</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
@@ -18193,7 +18277,7 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>OS West Main Ext</t>
+          <t>West Main Ext</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
@@ -18208,7 +18292,7 @@
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>OS West Main Ext</t>
+          <t>West Main Ext</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
@@ -18225,7 +18309,7 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>OS Main West</t>
+          <t>Main West</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
@@ -18240,7 +18324,7 @@
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>OS Main West</t>
+          <t>Main West</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
@@ -18257,7 +18341,7 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>OS S-4</t>
+          <t>Track S-4</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
@@ -18272,7 +18356,7 @@
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>OS S-4</t>
+          <t>Track S-4</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
@@ -18289,7 +18373,7 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>OS S-3</t>
+          <t>Track S-3</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
@@ -18304,7 +18388,7 @@
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>OS S-3</t>
+          <t>Track S-3</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
@@ -18321,7 +18405,7 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>OS S-2</t>
+          <t>Track S-2</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
@@ -18336,7 +18420,7 @@
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>OS S-2</t>
+          <t>Track S-2</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
@@ -18353,7 +18437,7 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>OS S-1</t>
+          <t>Track S-1</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
@@ -18368,7 +18452,7 @@
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>OS S-1</t>
+          <t>Track S-1</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
@@ -18385,7 +18469,7 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>OS S-R</t>
+          <t>Track S-R</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
@@ -18400,7 +18484,7 @@
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>OS S-R</t>
+          <t>Track S-R</t>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
@@ -18417,7 +18501,7 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>OS 13</t>
+          <t>OS Switch 13</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
@@ -18432,7 +18516,7 @@
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>OS 13</t>
+          <t>OS Switch 13</t>
         </is>
       </c>
       <c r="F16" s="3" t="inlineStr">
@@ -18449,7 +18533,7 @@
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>OS 15</t>
+          <t>OS Switch 15</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
@@ -18464,7 +18548,7 @@
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>OS 15</t>
+          <t>OS Switch 15</t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
@@ -18481,7 +18565,7 @@
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>OS 17</t>
+          <t>OS Switch 17</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
@@ -18496,7 +18580,7 @@
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>OS 17</t>
+          <t>OS Switch 17</t>
         </is>
       </c>
       <c r="F18" s="3" t="inlineStr">
@@ -18513,7 +18597,7 @@
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>OS 19</t>
+          <t>OS Switch 19</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
@@ -18528,7 +18612,7 @@
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>OS 19</t>
+          <t>OS Switch 19</t>
         </is>
       </c>
       <c r="F19" s="3" t="inlineStr">
@@ -18545,7 +18629,7 @@
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>OS 21</t>
+          <t>OS Switch 21</t>
         </is>
       </c>
       <c r="C20" s="3" t="inlineStr">
@@ -18560,7 +18644,7 @@
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>OS 21</t>
+          <t>OS Switch 21</t>
         </is>
       </c>
       <c r="F20" s="3" t="inlineStr">
@@ -18577,7 +18661,7 @@
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>OS 3</t>
+          <t>OS Switch 3</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
@@ -18592,7 +18676,7 @@
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>OS 3</t>
+          <t>OS Switch 3</t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr">
@@ -18609,7 +18693,7 @@
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>OS 1</t>
+          <t>OS Switch 1</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
@@ -18624,7 +18708,7 @@
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>OS 1</t>
+          <t>OS Switch 1</t>
         </is>
       </c>
       <c r="F22" s="3" t="inlineStr">
@@ -18641,7 +18725,7 @@
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>OS W-2</t>
+          <t>Track W-2</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
@@ -18656,7 +18740,7 @@
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>OS W-2</t>
+          <t>Track W-2</t>
         </is>
       </c>
       <c r="F23" s="3" t="inlineStr">
@@ -18673,7 +18757,7 @@
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>OS W-1</t>
+          <t>Track W-1</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
@@ -18688,7 +18772,7 @@
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>OS W-1</t>
+          <t>Track W-1</t>
         </is>
       </c>
       <c r="F24" s="3" t="inlineStr">
@@ -18705,7 +18789,7 @@
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>OS 5</t>
+          <t>OS Switch 5</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
@@ -18720,7 +18804,7 @@
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>OS 5</t>
+          <t>OS Switch 5</t>
         </is>
       </c>
       <c r="F25" s="3" t="inlineStr">
@@ -18737,7 +18821,7 @@
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>OS Brick-Plane</t>
+          <t>Track Brick-Plane</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
@@ -18752,7 +18836,7 @@
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t>OS Brick-Plane</t>
+          <t>Track Brick-Plane</t>
         </is>
       </c>
       <c r="F26" s="3" t="inlineStr">
@@ -18769,7 +18853,7 @@
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>OS East Main Ext</t>
+          <t>East Main Ext</t>
         </is>
       </c>
       <c r="C27" s="3" t="inlineStr">
@@ -18784,7 +18868,7 @@
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t>OS East Main Ext</t>
+          <t>East Main Ext</t>
         </is>
       </c>
       <c r="F27" s="3" t="inlineStr">
@@ -18801,7 +18885,7 @@
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>OS Scale</t>
+          <t>Track Scale</t>
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr">
@@ -18816,7 +18900,7 @@
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t>OS Scale</t>
+          <t>Track Scale</t>
         </is>
       </c>
       <c r="F28" s="3" t="inlineStr">
@@ -18833,7 +18917,7 @@
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>OS 25</t>
+          <t>OS Switch 25</t>
         </is>
       </c>
       <c r="C29" s="3" t="inlineStr">
@@ -18848,7 +18932,7 @@
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t>OS 25</t>
+          <t>OS Switch 25</t>
         </is>
       </c>
       <c r="F29" s="3" t="inlineStr">
@@ -18865,7 +18949,7 @@
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>OS 27</t>
+          <t>OS Switch 27</t>
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr">
@@ -18880,7 +18964,7 @@
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t>OS 27</t>
+          <t>OS Switch 27</t>
         </is>
       </c>
       <c r="F30" s="3" t="inlineStr">
@@ -18897,7 +18981,7 @@
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>OS 23a</t>
+          <t>OS Switch 23a</t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr">
@@ -18912,7 +18996,7 @@
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t>OS 23a</t>
+          <t>OS Switch 23a</t>
         </is>
       </c>
       <c r="F31" s="3" t="inlineStr">
@@ -18929,7 +19013,7 @@
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>OS 29</t>
+          <t>OS Switch 29</t>
         </is>
       </c>
       <c r="C32" s="3" t="inlineStr">
@@ -18944,7 +19028,7 @@
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
-          <t>OS 29</t>
+          <t>OS Switch 29</t>
         </is>
       </c>
       <c r="F32" s="3" t="inlineStr">
@@ -18961,7 +19045,7 @@
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>OS 23b</t>
+          <t>OS Switch 23b</t>
         </is>
       </c>
       <c r="C33" s="3" t="inlineStr">
@@ -18976,7 +19060,7 @@
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
-          <t>OS 23b</t>
+          <t>OS Switch 23b</t>
         </is>
       </c>
       <c r="F33" s="3" t="inlineStr">
@@ -18993,7 +19077,7 @@
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>OS 31</t>
+          <t>OS Switch 31</t>
         </is>
       </c>
       <c r="C34" s="3" t="inlineStr">
@@ -19008,7 +19092,7 @@
       </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
-          <t>OS 31</t>
+          <t>OS Switch 31</t>
         </is>
       </c>
       <c r="F34" s="3" t="inlineStr">
@@ -19025,7 +19109,7 @@
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>OS 33</t>
+          <t>OS Switch 33</t>
         </is>
       </c>
       <c r="C35" s="3" t="inlineStr">
@@ -19040,7 +19124,7 @@
       </c>
       <c r="E35" s="3" t="inlineStr">
         <is>
-          <t>OS 33</t>
+          <t>OS Switch 33</t>
         </is>
       </c>
       <c r="F35" s="3" t="inlineStr">
@@ -19057,7 +19141,7 @@
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>OS Barn</t>
+          <t>Track Barn</t>
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr">
@@ -19072,7 +19156,7 @@
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
-          <t>OS Barn</t>
+          <t>Track Barn</t>
         </is>
       </c>
       <c r="F36" s="3" t="inlineStr">
@@ -19089,7 +19173,7 @@
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>OS 11</t>
+          <t>OS Switch 11</t>
         </is>
       </c>
       <c r="C37" s="3" t="inlineStr">
@@ -19104,7 +19188,7 @@
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t>OS 11</t>
+          <t>OS Switch 11</t>
         </is>
       </c>
       <c r="F37" s="3" t="inlineStr">
@@ -19121,7 +19205,7 @@
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>OS 7</t>
+          <t>OS Switch 7</t>
         </is>
       </c>
       <c r="C38" s="3" t="inlineStr">
@@ -19136,7 +19220,7 @@
       </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
-          <t>OS 7</t>
+          <t>OS Switch 7</t>
         </is>
       </c>
       <c r="F38" s="3" t="inlineStr">
@@ -19153,7 +19237,7 @@
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>OS 7b</t>
+          <t>OS Switch 7b</t>
         </is>
       </c>
       <c r="C39" s="3" t="inlineStr">
@@ -19168,7 +19252,7 @@
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t>OS 7b</t>
+          <t>OS Switch 7b</t>
         </is>
       </c>
       <c r="F39" s="3" t="inlineStr">
@@ -19185,7 +19269,7 @@
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>OS EH-3</t>
+          <t>Track Scale1</t>
         </is>
       </c>
       <c r="C40" s="3" t="inlineStr">
@@ -19200,7 +19284,7 @@
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
-          <t>OS EH-3</t>
+          <t>Track Scale1</t>
         </is>
       </c>
       <c r="F40" s="3" t="inlineStr">
@@ -19217,7 +19301,7 @@
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>OS EH-2</t>
+          <t>Track Scale0</t>
         </is>
       </c>
       <c r="C41" s="3" t="inlineStr">
@@ -19232,7 +19316,7 @@
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
-          <t>OS EH-2</t>
+          <t>Track Scale0</t>
         </is>
       </c>
       <c r="F41" s="3" t="inlineStr">
@@ -19249,7 +19333,7 @@
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>OS EH-1</t>
+          <t>Yard T9</t>
         </is>
       </c>
       <c r="C42" s="3" t="inlineStr">
@@ -19264,7 +19348,7 @@
       </c>
       <c r="E42" s="3" t="inlineStr">
         <is>
-          <t>OS EH-1</t>
+          <t>Yard T9</t>
         </is>
       </c>
       <c r="F42" s="3" t="inlineStr">
@@ -19281,7 +19365,7 @@
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>OS 9</t>
+          <t>OS Switch 9</t>
         </is>
       </c>
       <c r="C43" s="3" t="inlineStr">
@@ -19296,7 +19380,7 @@
       </c>
       <c r="E43" s="3" t="inlineStr">
         <is>
-          <t>OS 9</t>
+          <t>OS Switch 9</t>
         </is>
       </c>
       <c r="F43" s="3" t="inlineStr">

--- a/cats/data/signals_asbuilt_abs_v2.xlsx
+++ b/cats/data/signals_asbuilt_abs_v2.xlsx
@@ -1280,7 +1280,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>C4</t>
+          <t>C3</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -1290,7 +1290,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>C4-OU2-1 C4-OU2-3 C4-OU2-2</t>
+          <t>C3-OU2-1 C3-OU2-3 C3-OU2-2</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -1355,7 +1355,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>C4</t>
+          <t>C3</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -1365,7 +1365,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>C4-OU2-4 C4-OU2-6 C4-OU2-5</t>
+          <t>C3-OU2-4 C3-OU2-6 C3-OU2-5</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1430,7 +1430,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>C4</t>
+          <t>C3</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -1440,7 +1440,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>C4-OU3-4 C4-OU3-6 C4-OU3-5</t>
+          <t>C3-OU3-4 C3-OU3-6 C3-OU3-5</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1505,7 +1505,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>C4</t>
+          <t>C3</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1515,7 +1515,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>C4-OU3-7 C4-OU3-8 C4-OU2-7</t>
+          <t>C3-OU3-7 C3-OU3-8 C3-OU2-7</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1580,7 +1580,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>C4</t>
+          <t>C3</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1590,7 +1590,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>C4-OU3-1 C4-OU3-3 C4-OU3-2</t>
+          <t>C3-OU3-1 C3-OU3-3 C3-OU3-2</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1655,7 +1655,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>C5</t>
+          <t>C13</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1665,7 +1665,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>C5-OU1-1 C5-OU1-3 C5-OU1-2</t>
+          <t>C13-OU1-1 C13-OU1-3 C13-OU1-2</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1730,7 +1730,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>C5</t>
+          <t>C13</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1740,7 +1740,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>C5-OU1-4 C5-OU1-5 C5-OU1-6</t>
+          <t>C13-OU1-4 C13-OU1-5 C13-OU1-6</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -1805,7 +1805,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>C5</t>
+          <t>C13</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1815,7 +1815,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>C5-OU2-1 C5-OU2-3 C5-OU2-2</t>
+          <t>C13-OU2-1 C13-OU2-3 C13-OU2-2</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -1880,7 +1880,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>C5</t>
+          <t>C13</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1890,7 +1890,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>C5-OU2-4 C5-OU2-6 C5-OU2-5</t>
+          <t>C13-OU2-4 C13-OU2-6 C13-OU2-5</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>C3</t>
+          <t>C2</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1965,7 +1965,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>C3-OU1-1 C3-OU1-3 C3-OU1-2</t>
+          <t>C2-OU1-1 C2-OU1-3 C2-OU1-2</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1990,7 +1990,7 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>LCOS Signal 0 UID 32; STOP/APPROACH/CLEAR; lamp G; was C3-OU1 new 5V</t>
+          <t>LCOS Signal 0 UID 32; STOP/APPROACH/CLEAR; lamp G; was C2-OU1 5V (was C3)</t>
         </is>
       </c>
     </row>
@@ -2030,7 +2030,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>C3</t>
+          <t>C2</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -2040,7 +2040,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>C3-OU1-4 C3-OU1-6 C3-OU1-5</t>
+          <t>C2-OU1-4 C2-OU1-6 C2-OU1-5</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -2065,7 +2065,7 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>LCOS Signal 1 UID 33; STOP/APPROACH/CLEAR; lamp G; was C3-OU1 new 5V</t>
+          <t>LCOS Signal 1 UID 33; STOP/APPROACH/CLEAR; lamp G; was C2-OU1 5V (was C3)</t>
         </is>
       </c>
     </row>
@@ -2105,7 +2105,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>C3</t>
+          <t>C2</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>C3-OU1-7 C3-OU2-1 C3-OU1-8</t>
+          <t>C2-OU1-7 C2-OU2-1 C2-OU1-8</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -2180,7 +2180,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>C3</t>
+          <t>C2</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -2190,7 +2190,7 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>C3-OU2-2 C3-OU2-4 C3-OU2-3</t>
+          <t>C2-OU2-2 C2-OU2-4 C2-OU2-3</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -2255,7 +2255,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>C3</t>
+          <t>C2</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -2265,7 +2265,7 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>C3-OU2-5 C3-OU2-7 C3-OU2-6</t>
+          <t>C2-OU2-5 C2-OU2-7 C2-OU2-6</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -2330,7 +2330,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>C3</t>
+          <t>C2</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -2340,7 +2340,7 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>C3-OU3-1 C3-OU3-3 C3-OU3-2</t>
+          <t>C2-OU3-1 C2-OU3-3 C2-OU3-2</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -2780,7 +2780,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>C7</t>
+          <t>C11</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -2790,7 +2790,7 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>C7-OU2-1 C7-OU2-2 C7-OU2-3</t>
+          <t>C11-OU2-1 C11-OU2-2 C11-OU2-3</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -2851,7 +2851,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>C7</t>
+          <t>C11</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -2861,7 +2861,7 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>C7-OU2-4 C7-OU2-5 C7-OU2-6</t>
+          <t>C11-OU2-4 C11-OU2-5 C11-OU2-6</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -2922,7 +2922,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>C7</t>
+          <t>C11</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -2932,7 +2932,7 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>C7-OU3-1 C7-OU3-2 C7-OU3-3</t>
+          <t>C11-OU3-1 C11-OU3-2 C11-OU3-3</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">

--- a/cats/data/signals_asbuilt_abs_v2.xlsx
+++ b/cats/data/signals_asbuilt_abs_v2.xlsx
@@ -1256,7 +1256,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1285,32 +1285,32 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>432</t>
+          <t>432 433</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>C3-OU2-1 C3-OU2-3 C3-OU2-2</t>
+          <t>C3-OU2-1 C3-OU2-3 C3-OU2-2 C3-OU4-1 C3-OU4-3 C3-OU4-2</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>track/signalhead/432</t>
+          <t>track/signalhead/432 track/signalhead/433</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>IF$shsm:AAR-1946:SL-1-low(IH432)</t>
+          <t>IF$shsm:hart-aar:SL-2-digicon(IH432)(IH433)</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>single</t>
+          <t>double</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>AAR-1946 SL-1-low (3-pin STOP/APPROACH/CLEAR)</t>
+          <t>hart-aar SL-2-digicon (two 3-pin STOP/APPROACH/CLEAR discs)</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -1556,7 +1556,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1585,32 +1585,32 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>438</t>
+          <t>438 439</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>C3-OU3-1 C3-OU3-3 C3-OU3-2</t>
+          <t>C3-OU3-1 C3-OU3-3 C3-OU3-2 C3-OU4-4 C3-OU4-6 C3-OU4-5</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>track/signalhead/438</t>
+          <t>track/signalhead/438 track/signalhead/439</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>IF$shsm:AAR-1946:SL-1-low(IH438)</t>
+          <t>IF$shsm:hart-aar:SL-2-digicon(IH438)(IH439)</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>single</t>
+          <t>double</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>AAR-1946 SL-1-low (3-pin STOP/APPROACH/CLEAR)</t>
+          <t>hart-aar SL-2-digicon (two 3-pin STOP/APPROACH/CLEAR discs)</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -1631,7 +1631,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1660,32 +1660,32 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1332</t>
+          <t>1332 1333</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>C13-OU1-1 C13-OU1-3 C13-OU1-2</t>
+          <t>C13-OU1-1 C13-OU1-3 C13-OU1-2 C13-OU4-1 C13-OU4-3 C13-OU4-2</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>track/signalhead/1332</t>
+          <t>track/signalhead/1332 track/signalhead/1333</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>IF$shsm:AAR-1946:SL-1-low(IH1332)</t>
+          <t>IF$shsm:hart-aar:SL-2-digicon(IH1332)(IH1333)</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>single</t>
+          <t>double</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>AAR-1946 SL-1-low (3-pin STOP/APPROACH/CLEAR)</t>
+          <t>hart-aar SL-2-digicon (two 3-pin STOP/APPROACH/CLEAR discs)</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -1706,7 +1706,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1735,32 +1735,32 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1335</t>
+          <t>1335 1336</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>C13-OU1-4 C13-OU1-5 C13-OU1-6</t>
+          <t>C13-OU1-4 C13-OU1-5 C13-OU1-6 C13-OU4-4 C13-OU4-6 C13-OU4-5</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>track/signalhead/1335</t>
+          <t>track/signalhead/1335 track/signalhead/1336</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>IF$shsm:AAR-1946:SL-1-low(IH1335)</t>
+          <t>IF$shsm:hart-aar:SL-2-digicon(IH1335)(IH1336)</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>single</t>
+          <t>double</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>AAR-1946 SL-1-low (3-pin STOP/APPROACH/CLEAR)</t>
+          <t>hart-aar SL-2-digicon (two 3-pin STOP/APPROACH/CLEAR discs)</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -1856,7 +1856,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1885,32 +1885,32 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1337</t>
+          <t>1337 1338</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>C13-OU2-4 C13-OU2-6 C13-OU2-5</t>
+          <t>C13-OU2-4 C13-OU2-6 C13-OU2-5 C13-OU4-7 C13-OU2-8 C13-OU4-8</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>track/signalhead/1337</t>
+          <t>track/signalhead/1337 track/signalhead/1338</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>IF$shsm:AAR-1946:SL-1-low(IH1337)</t>
+          <t>IF$shsm:hart-aar:SL-2-digicon(IH1337)(IH1338)</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>single</t>
+          <t>double</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>AAR-1946 SL-1-low (3-pin STOP/APPROACH/CLEAR)</t>
+          <t>hart-aar SL-2-digicon (two 3-pin STOP/APPROACH/CLEAR discs)</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -1931,7 +1931,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1960,37 +1960,37 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>232</t>
+          <t>232 238</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>C2-OU1-1 C2-OU1-3 C2-OU1-2</t>
+          <t>C2-OU1-1 C2-OU1-3 C2-OU1-2 C2-OU4-1 C2-OU4-3 C2-OU4-2</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>track/signalhead/232</t>
+          <t>track/signalhead/232 track/signalhead/238</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>IF$shsm:AAR-1946:SL-1-low(IH232)</t>
+          <t>IF$shsm:hart-aar:SL-2-digicon(IH232)(IH238)</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>single</t>
+          <t>double</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>AAR-1946 SL-1-low (3-pin STOP/APPROACH/CLEAR)</t>
+          <t>hart-aar SL-2-digicon (two 3-pin STOP/APPROACH/CLEAR discs)</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>LCOS Signal 0 UID 32; STOP/APPROACH/CLEAR; lamp G; was C2-OU1 5V (was C3)</t>
+          <t>LCOS Signal 0 UID 32; STOP/APPROACH/CLEAR; lamp G; was C2-OU1 5V</t>
         </is>
       </c>
     </row>
@@ -2006,7 +2006,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2035,37 +2035,37 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>233</t>
+          <t>233 239</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>C2-OU1-4 C2-OU1-6 C2-OU1-5</t>
+          <t>C2-OU1-4 C2-OU1-6 C2-OU1-5 C2-OU4-4 C2-OU4-6 C2-OU4-5</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>track/signalhead/233</t>
+          <t>track/signalhead/233 track/signalhead/239</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>IF$shsm:AAR-1946:SL-1-low(IH233)</t>
+          <t>IF$shsm:hart-aar:SL-2-digicon(IH233)(IH239)</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>single</t>
+          <t>double</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>AAR-1946 SL-1-low (3-pin STOP/APPROACH/CLEAR)</t>
+          <t>hart-aar SL-2-digicon (two 3-pin STOP/APPROACH/CLEAR discs)</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>LCOS Signal 1 UID 33; STOP/APPROACH/CLEAR; lamp G; was C2-OU1 5V (was C3)</t>
+          <t>LCOS Signal 1 UID 33; STOP/APPROACH/CLEAR; lamp G; was C2-OU1 5V</t>
         </is>
       </c>
     </row>
@@ -2156,7 +2156,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2185,32 +2185,32 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>235</t>
+          <t>235 240</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>C2-OU2-2 C2-OU2-4 C2-OU2-3</t>
+          <t>C2-OU2-2 C2-OU2-4 C2-OU2-3 C2-OU4-7 C2-OU3-7 C2-OU4-8</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>track/signalhead/235</t>
+          <t>track/signalhead/235 track/signalhead/240</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>IF$shsm:AAR-1946:SL-1-low(IH235)</t>
+          <t>IF$shsm:hart-aar:SL-2-digicon(IH235)(IH240)</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>single</t>
+          <t>double</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>AAR-1946 SL-1-low (3-pin STOP/APPROACH/CLEAR)</t>
+          <t>hart-aar SL-2-digicon (two 3-pin STOP/APPROACH/CLEAR discs)</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
@@ -2306,7 +2306,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2335,32 +2335,32 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>237</t>
+          <t>237 241</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>C2-OU3-1 C2-OU3-3 C2-OU3-2</t>
+          <t>C2-OU3-1 C2-OU3-3 C2-OU3-2 C2-OU3-4 C2-OU3-6 C2-OU3-5</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>track/signalhead/237</t>
+          <t>track/signalhead/237 track/signalhead/241</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>IF$shsm:AAR-1946:SL-1-low(IH237)</t>
+          <t>IF$shsm:hart-aar:SL-2-digicon(IH237)(IH241)</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>single</t>
+          <t>double</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>AAR-1946 SL-1-low (3-pin STOP/APPROACH/CLEAR)</t>
+          <t>hart-aar SL-2-digicon (two 3-pin STOP/APPROACH/CLEAR discs)</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
@@ -2381,7 +2381,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2410,32 +2410,32 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>132</t>
+          <t>132 133</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>C1-OU2-1 C1-OU2-3 C1-OU2-2</t>
+          <t>C1-OU2-1 C1-OU2-3 C1-OU2-2 C1-OU4-1 C1-OU4-3 C1-OU4-2</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>track/signalhead/132</t>
+          <t>track/signalhead/132 track/signalhead/133</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>IF$shsm:AAR-1946:SL-1-low(IH132)</t>
+          <t>IF$shsm:hart-aar:SL-2-digicon(IH132)(IH133)</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>single</t>
+          <t>double</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>AAR-1946 SL-1-low (3-pin STOP/APPROACH/CLEAR)</t>
+          <t>hart-aar SL-2-digicon (two 3-pin STOP/APPROACH/CLEAR discs)</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
@@ -2456,7 +2456,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2485,32 +2485,32 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>135</t>
+          <t>135 136</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>C1-OU2-4 C1-OU2-6 C1-OU2-5</t>
+          <t>C1-OU2-4 C1-OU2-6 C1-OU2-5 C1-OU4-4 C1-OU4-6 C1-OU4-5</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>track/signalhead/135</t>
+          <t>track/signalhead/135 track/signalhead/136</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>IF$shsm:AAR-1946:SL-1-low(IH135)</t>
+          <t>IF$shsm:hart-aar:SL-2-digicon(IH135)(IH136)</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>single</t>
+          <t>double</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>AAR-1946 SL-1-low (3-pin STOP/APPROACH/CLEAR)</t>
+          <t>hart-aar SL-2-digicon (two 3-pin STOP/APPROACH/CLEAR discs)</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
@@ -2531,7 +2531,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2560,32 +2560,32 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>139</t>
+          <t>139 140</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>C1-OU3-1 C1-OU3-3 C1-OU3-2</t>
+          <t>C1-OU3-1 C1-OU3-3 C1-OU3-2 C1-OU4-7 C1-OU2-8 C1-OU4-8</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>track/signalhead/139</t>
+          <t>track/signalhead/139 track/signalhead/140</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>IF$shsm:AAR-1946:SL-1-low(IH139)</t>
+          <t>IF$shsm:hart-aar:SL-2-digicon(IH139)(IH140)</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>single</t>
+          <t>double</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>AAR-1946 SL-1-low (3-pin STOP/APPROACH/CLEAR)</t>
+          <t>hart-aar SL-2-digicon (two 3-pin STOP/APPROACH/CLEAR discs)</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
@@ -2756,7 +2756,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2785,32 +2785,32 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>1132</t>
+          <t>1132 1135</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>C11-OU2-1 C11-OU2-2 C11-OU2-3</t>
+          <t>C11-OU2-1 C11-OU2-2 C11-OU2-3 C11-OU3-4 C11-OU3-6 C11-OU3-5</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>track/signalhead/1132</t>
+          <t>track/signalhead/1132 track/signalhead/1135</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>IF$shsm:AAR-1946:SL-1-low(IH1132)</t>
+          <t>IF$shsm:hart-aar:SL-2-digicon(IH1132)(IH1135)</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>single</t>
+          <t>double</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>AAR-1946 SL-1-low (3-pin STOP/APPROACH/CLEAR)</t>
+          <t>hart-aar SL-2-digicon (two 3-pin STOP/APPROACH/CLEAR discs)</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">

--- a/cats/data/signals_asbuilt_abs_v2.xlsx
+++ b/cats/data/signals_asbuilt_abs_v2.xlsx
@@ -1290,7 +1290,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>C3-OU2-1 C3-OU2-3 C3-OU2-2 C3-OU4-1 C3-OU4-3 C3-OU4-2</t>
+          <t>C3-OU2-1 C3-OU2-3 C3-OU2-2 C3-OU2-4 C3-OU2-6 C3-OU2-5</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -1365,7 +1365,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>C3-OU2-4 C3-OU2-6 C3-OU2-5</t>
+          <t>C3-OU2-7 C3-OU3-7 C3-OU2-8</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1390,7 +1390,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>LCOS Signal 2 UID 34; STOP/APPROACH/CLEAR; lamp G; was S3-7 G/Y/R</t>
+          <t>LCOS Signal 2 UID 34; STOP/APPROACH/CLEAR; lamp G; was G/Y on Plane OU2; R spills to 2L OU3</t>
         </is>
       </c>
     </row>
@@ -1402,25 +1402,25 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Mast 4RA</t>
+          <t>Mast 2L</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>(4,3) LEFT</t>
+          <t>(8,3) RIGHT</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Switch 3</t>
+          <t>Switch 1</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1435,37 +1435,37 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>436</t>
+          <t>438 439</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>C3-OU3-4 C3-OU3-6 C3-OU3-5</t>
+          <t>C3-OU3-1 C3-OU3-3 C3-OU3-2 C3-OU3-4 C3-OU3-6 C3-OU3-5</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>track/signalhead/436</t>
+          <t>track/signalhead/438 track/signalhead/439</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>IF$shsm:AAR-1946:SL-1-low(IH436)</t>
+          <t>IF$shsm:hart-aar:SL-2-digicon(IH438)(IH439)</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>single</t>
+          <t>double</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>AAR-1946 SL-1-low (3-pin STOP/APPROACH/CLEAR)</t>
+          <t>hart-aar SL-2-digicon (two 3-pin STOP/APPROACH/CLEAR discs)</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>LCOS Signal 4 UID 36; STOP/APPROACH/CLEAR; lamp G; was S3-9 G/Y/R</t>
+          <t>LCOS Signal 6 UID 38; STOP/APPROACH/CLEAR; lamp G; was S3-8 G/Y/R</t>
         </is>
       </c>
     </row>
@@ -1477,7 +1477,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Mast 4RB</t>
+          <t>Mast 4RA</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -1490,7 +1490,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>(4,4) LEFT</t>
+          <t>(4,3) LEFT</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -1510,22 +1510,22 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>437</t>
+          <t>436</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>C3-OU3-7 C3-OU3-8 C3-OU2-7</t>
+          <t>C3-OU4-1 C3-OU4-3 C3-OU4-2</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>track/signalhead/437</t>
+          <t>track/signalhead/436</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>IF$shsm:AAR-1946:SL-1-low(IH437)</t>
+          <t>IF$shsm:AAR-1946:SL-1-low(IH436)</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -1540,7 +1540,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>LCOS Signal 5 UID 37; STOP/APPROACH/CLEAR; lamp G; was S3-11 G/Y/R (Y on OU2-7)</t>
+          <t>LCOS Signal 4 UID 36; STOP/APPROACH/CLEAR; lamp G; was Brick west OU4 with 4RB</t>
         </is>
       </c>
     </row>
@@ -1552,25 +1552,25 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Mast 2L</t>
+          <t>Mast 4RB</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>(8,3) RIGHT</t>
+          <t>(4,4) LEFT</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Switch 1</t>
+          <t>Switch 3</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -1585,37 +1585,37 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>438 439</t>
+          <t>437</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>C3-OU3-1 C3-OU3-3 C3-OU3-2 C3-OU4-4 C3-OU4-6 C3-OU4-5</t>
+          <t>C3-OU4-4 C3-OU4-6 C3-OU4-5</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>track/signalhead/438 track/signalhead/439</t>
+          <t>track/signalhead/437</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>IF$shsm:hart-aar:SL-2-digicon(IH438)(IH439)</t>
+          <t>IF$shsm:AAR-1946:SL-1-low(IH437)</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>double</t>
+          <t>single</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>hart-aar SL-2-digicon (two 3-pin STOP/APPROACH/CLEAR discs)</t>
+          <t>AAR-1946 SL-1-low (3-pin STOP/APPROACH/CLEAR)</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>LCOS Signal 6 UID 38; STOP/APPROACH/CLEAR; lamp G; was S3-8 G/Y/R</t>
+          <t>LCOS Signal 5 UID 37; STOP/APPROACH/CLEAR; lamp G; was Brick west OU4 with 4RA</t>
         </is>
       </c>
     </row>
@@ -1665,7 +1665,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>C13-OU1-1 C13-OU1-3 C13-OU1-2 C13-OU4-1 C13-OU4-3 C13-OU4-2</t>
+          <t>C13-OU1-1 C13-OU1-3 C13-OU1-2 C13-OU1-4 C13-OU1-6 C13-OU1-5</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1740,7 +1740,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>C13-OU1-4 C13-OU1-5 C13-OU1-6 C13-OU4-4 C13-OU4-6 C13-OU4-5</t>
+          <t>C13-OU4-1 C13-OU4-3 C13-OU4-2 C13-OU4-4 C13-OU4-6 C13-OU4-5</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -1765,7 +1765,7 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>LCOS Signal 3 UID 35; STOP/APPROACH/CLEAR; lamp G; was S3-12 G/R/Y silk</t>
+          <t>LCOS Signal 3 UID 35; STOP/APPROACH/CLEAR; lamp G; was S3-12; sequential G/Y/R</t>
         </is>
       </c>
     </row>
@@ -1777,11 +1777,11 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Mast 8LB</t>
+          <t>Mast 8LA</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1790,7 +1790,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>(14,7) RIGHT</t>
+          <t>(14,8) RIGHT</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -1810,37 +1810,37 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1334</t>
+          <t>1337 1338</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>C13-OU2-1 C13-OU2-3 C13-OU2-2</t>
+          <t>C13-OU2-1 C13-OU2-3 C13-OU2-2 C13-OU2-4 C13-OU2-6 C13-OU2-5</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>track/signalhead/1334</t>
+          <t>track/signalhead/1337 track/signalhead/1338</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>IF$shsm:AAR-1946:SL-1-low(IH1334)</t>
+          <t>IF$shsm:hart-aar:SL-2-digicon(IH1337)(IH1338)</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>single</t>
+          <t>double</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>AAR-1946 SL-1-low (3-pin STOP/APPROACH/CLEAR)</t>
+          <t>hart-aar SL-2-digicon (two 3-pin STOP/APPROACH/CLEAR discs)</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>LCOS Signal 2 UID 34; STOP/APPROACH/CLEAR; lamp G; was S3-4 G/Y/R</t>
+          <t>LCOS Signal 5 UID 37; STOP/APPROACH/CLEAR; lamp G; was S3-5 G/Y/R</t>
         </is>
       </c>
     </row>
@@ -1852,11 +1852,11 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Mast 8LA</t>
+          <t>Mast 8LB</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1865,7 +1865,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>(14,8) RIGHT</t>
+          <t>(14,7) RIGHT</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1885,37 +1885,37 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1337 1338</t>
+          <t>1334</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>C13-OU2-4 C13-OU2-6 C13-OU2-5 C13-OU4-7 C13-OU2-8 C13-OU4-8</t>
+          <t>C13-OU2-7 C13-OU4-7 C13-OU2-8</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>track/signalhead/1337 track/signalhead/1338</t>
+          <t>track/signalhead/1334</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>IF$shsm:hart-aar:SL-2-digicon(IH1337)(IH1338)</t>
+          <t>IF$shsm:AAR-1946:SL-1-low(IH1334)</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>double</t>
+          <t>single</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>hart-aar SL-2-digicon (two 3-pin STOP/APPROACH/CLEAR discs)</t>
+          <t>AAR-1946 SL-1-low (3-pin STOP/APPROACH/CLEAR)</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>LCOS Signal 5 UID 37; STOP/APPROACH/CLEAR; lamp G; was S3-5 G/Y/R</t>
+          <t>LCOS Signal 2 UID 34; STOP/APPROACH/CLEAR; lamp G; was G/Y with 8LA; R spills to 8RB OU4</t>
         </is>
       </c>
     </row>
@@ -1965,7 +1965,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>C2-OU1-1 C2-OU1-3 C2-OU1-2 C2-OU4-1 C2-OU4-3 C2-OU4-2</t>
+          <t>C2-OU1-1 C2-OU1-3 C2-OU1-2 C2-OU1-4 C2-OU1-6 C2-OU1-5</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -2002,20 +2002,20 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Mast 24L</t>
+          <t>Mast 24RB</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>(30,6) RIGHT</t>
+          <t>(28,7) LEFT</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -2035,37 +2035,37 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>233 239</t>
+          <t>234</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>C2-OU1-4 C2-OU1-6 C2-OU1-5 C2-OU4-4 C2-OU4-6 C2-OU4-5</t>
+          <t>C2-OU1-7 C2-OU2-7 C2-OU1-8</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>track/signalhead/233 track/signalhead/239</t>
+          <t>track/signalhead/234</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>IF$shsm:hart-aar:SL-2-digicon(IH233)(IH239)</t>
+          <t>IF$shsm:AAR-1946:SL-1-low(IH234)</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>double</t>
+          <t>single</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>hart-aar SL-2-digicon (two 3-pin STOP/APPROACH/CLEAR discs)</t>
+          <t>AAR-1946 SL-1-low (3-pin STOP/APPROACH/CLEAR)</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>LCOS Signal 1 UID 33; STOP/APPROACH/CLEAR; lamp G; was C2-OU1 5V</t>
+          <t>LCOS Signal 2 UID 34; STOP/APPROACH/CLEAR; lamp G; was G/Y with 24RA; R spills to 24L OU2</t>
         </is>
       </c>
     </row>
@@ -2077,20 +2077,20 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Mast 24RB</t>
+          <t>Mast 24L</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>(28,7) LEFT</t>
+          <t>(30,6) RIGHT</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -2110,37 +2110,37 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>234</t>
+          <t>233 239</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>C2-OU1-7 C2-OU2-1 C2-OU1-8</t>
+          <t>C2-OU2-1 C2-OU2-3 C2-OU2-2 C2-OU2-4 C2-OU2-6 C2-OU2-5</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>track/signalhead/234</t>
+          <t>track/signalhead/233 track/signalhead/239</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>IF$shsm:AAR-1946:SL-1-low(IH234)</t>
+          <t>IF$shsm:hart-aar:SL-2-digicon(IH233)(IH239)</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>single</t>
+          <t>double</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>AAR-1946 SL-1-low (3-pin STOP/APPROACH/CLEAR)</t>
+          <t>hart-aar SL-2-digicon (two 3-pin STOP/APPROACH/CLEAR discs)</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>LCOS Signal 2 UID 34; STOP/APPROACH/CLEAR; lamp G; was OU1-7/8 + OU2-1</t>
+          <t>LCOS Signal 1 UID 33; STOP/APPROACH/CLEAR; lamp G; was moved from OU1 with 24RA</t>
         </is>
       </c>
     </row>
@@ -2190,7 +2190,7 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>C2-OU2-2 C2-OU2-4 C2-OU2-3 C2-OU4-7 C2-OU3-7 C2-OU4-8</t>
+          <t>C2-OU3-1 C2-OU3-3 C2-OU3-2 C2-OU3-4 C2-OU3-6 C2-OU3-5</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -2265,7 +2265,7 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>C2-OU2-5 C2-OU2-7 C2-OU2-6</t>
+          <t>C2-OU3-7 C2-OU4-7 C2-OU3-8</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -2290,7 +2290,7 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>LCOS Signal 4 UID 36; STOP/APPROACH/CLEAR; lamp G; was OU2-8 is relay</t>
+          <t>LCOS Signal 4 UID 36; STOP/APPROACH/CLEAR; lamp G; was G/Y with 34L; R spills to 34R OU4</t>
         </is>
       </c>
     </row>
@@ -2340,7 +2340,7 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>C2-OU3-1 C2-OU3-3 C2-OU3-2 C2-OU3-4 C2-OU3-6 C2-OU3-5</t>
+          <t>C2-OU4-1 C2-OU4-3 C2-OU4-2 C2-OU4-4 C2-OU4-6 C2-OU4-5</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -2377,7 +2377,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Mast 40LB</t>
+          <t>Mast 36RA</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -2385,17 +2385,17 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>(43,5) RIGHT</t>
+          <t>(37,6) LEFT</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Switch 39</t>
+          <t>Switch 35</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -2410,22 +2410,22 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>132 133</t>
+          <t>135 136</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>C1-OU2-1 C1-OU2-3 C1-OU2-2 C1-OU4-1 C1-OU4-3 C1-OU4-2</t>
+          <t>C1-OU2-1 C1-OU2-3 C1-OU2-2 C1-OU2-4 C1-OU2-6 C1-OU2-5</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>track/signalhead/132 track/signalhead/133</t>
+          <t>track/signalhead/135 track/signalhead/136</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>IF$shsm:hart-aar:SL-2-digicon(IH132)(IH133)</t>
+          <t>IF$shsm:hart-aar:SL-2-digicon(IH135)(IH136)</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -2440,7 +2440,7 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>LCOS Signal 0 UID 32; STOP/APPROACH/CLEAR; lamp G; was S1-1 G/Y/R</t>
+          <t>LCOS Signal 3 UID 35; STOP/APPROACH/CLEAR; lamp G; was S1-2 G/Y/R</t>
         </is>
       </c>
     </row>
@@ -2452,11 +2452,11 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Mast 36RA</t>
+          <t>Mast 40LA</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2465,12 +2465,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>(37,6) LEFT</t>
+          <t>(43,6) RIGHT</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Switch 35</t>
+          <t>Switch 39</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -2485,37 +2485,37 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>135 136</t>
+          <t>142</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>C1-OU2-4 C1-OU2-6 C1-OU2-5 C1-OU4-4 C1-OU4-6 C1-OU4-5</t>
+          <t>C1-OU3-7 C1-OU2-7 C1-OU3-8</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>track/signalhead/135 track/signalhead/136</t>
+          <t>track/signalhead/142</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>IF$shsm:hart-aar:SL-2-digicon(IH135)(IH136)</t>
+          <t>IF$shsm:AAR-1946:SL-1-low(IH142)</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>double</t>
+          <t>single</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>hart-aar SL-2-digicon (two 3-pin STOP/APPROACH/CLEAR discs)</t>
+          <t>AAR-1946 SL-1-low (3-pin STOP/APPROACH/CLEAR)</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>LCOS Signal 3 UID 35; STOP/APPROACH/CLEAR; lamp G; was S1-2 G/Y/R</t>
+          <t>LCOS Signal 10 UID 42; STOP/APPROACH/CLEAR; lamp G; was G/Y with 40LB; R spills to 36RA OU2</t>
         </is>
       </c>
     </row>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Mast 38LB</t>
+          <t>Mast 40LB</t>
         </is>
       </c>
       <c r="C19" t="n">
@@ -2540,12 +2540,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>(43,8) RIGHT</t>
+          <t>(43,5) RIGHT</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Switch 37</t>
+          <t>Switch 39</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -2560,22 +2560,22 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>139 140</t>
+          <t>132 133</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>C1-OU3-1 C1-OU3-3 C1-OU3-2 C1-OU4-7 C1-OU2-8 C1-OU4-8</t>
+          <t>C1-OU3-1 C1-OU3-3 C1-OU3-2 C1-OU3-4 C1-OU3-6 C1-OU3-5</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>track/signalhead/139 track/signalhead/140</t>
+          <t>track/signalhead/132 track/signalhead/133</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>IF$shsm:hart-aar:SL-2-digicon(IH139)(IH140)</t>
+          <t>IF$shsm:hart-aar:SL-2-digicon(IH132)(IH133)</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -2590,7 +2590,7 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>LCOS Signal 7 UID 39; STOP/APPROACH/CLEAR; lamp G; was S1-3 G/Y/R</t>
+          <t>LCOS Signal 0 UID 32; STOP/APPROACH/CLEAR; lamp G; was S1-1 G/Y/R</t>
         </is>
       </c>
     </row>
@@ -2602,7 +2602,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Mast 40LA</t>
+          <t>Mast 38LA</t>
         </is>
       </c>
       <c r="C20" t="n">
@@ -2615,12 +2615,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>(43,6) RIGHT</t>
+          <t>(43,7) RIGHT</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Switch 39</t>
+          <t>Switch 37</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -2635,22 +2635,22 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>142</t>
+          <t>143</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>C1-OU3-4 C1-OU3-6 C1-OU3-5</t>
+          <t>C1-OU4-7 C1-OU2-8 C1-OU4-8</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>track/signalhead/142</t>
+          <t>track/signalhead/143</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>IF$shsm:AAR-1946:SL-1-low(IH142)</t>
+          <t>IF$shsm:AAR-1946:SL-1-low(IH143)</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -2665,7 +2665,7 @@
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>LCOS Signal 10 UID 42; STOP/APPROACH/CLEAR; lamp G; was S1-4 G/Y/R</t>
+          <t>LCOS Signal 11 UID 43; STOP/APPROACH/CLEAR; lamp G; was G/Y with 38LB; R spills to 36RA OU2</t>
         </is>
       </c>
     </row>
@@ -2677,20 +2677,20 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Mast 38LA</t>
+          <t>Mast 38LB</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>(43,7) RIGHT</t>
+          <t>(43,8) RIGHT</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -2710,37 +2710,37 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>143</t>
+          <t>139 140</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>C1-OU2-7 C1-OU3-8 C1-OU3-7</t>
+          <t>C1-OU4-1 C1-OU4-3 C1-OU4-2 C1-OU4-4 C1-OU4-6 C1-OU4-5</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>track/signalhead/143</t>
+          <t>track/signalhead/139 track/signalhead/140</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>IF$shsm:AAR-1946:SL-1-low(IH143)</t>
+          <t>IF$shsm:hart-aar:SL-2-digicon(IH139)(IH140)</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>single</t>
+          <t>double</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>AAR-1946 SL-1-low (3-pin STOP/APPROACH/CLEAR)</t>
+          <t>hart-aar SL-2-digicon (two 3-pin STOP/APPROACH/CLEAR discs)</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>LCOS Signal 11 UID 43; STOP/APPROACH/CLEAR; lamp G; was spares G/Y/R</t>
+          <t>LCOS Signal 7 UID 39; STOP/APPROACH/CLEAR; lamp G; was S1-3 G/Y/R</t>
         </is>
       </c>
     </row>
@@ -2790,7 +2790,7 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>C11-OU2-1 C11-OU2-2 C11-OU2-3 C11-OU3-4 C11-OU3-6 C11-OU3-5</t>
+          <t>C11-OU2-1 C11-OU2-3 C11-OU2-2 C11-OU2-4 C11-OU2-6 C11-OU2-5</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -2815,7 +2815,7 @@
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>LCOS Signal 0 UID 32; STOP/APPROACH/CLEAR; lamp G; was S1-5 G/R/Y silk</t>
+          <t>LCOS Signal 0 UID 32; STOP/APPROACH/CLEAR; lamp G; was S1-5; sequential G/Y/R</t>
         </is>
       </c>
     </row>
@@ -2861,7 +2861,7 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>C11-OU2-4 C11-OU2-5 C11-OU2-6</t>
+          <t>C11-OU3-1 C11-OU3-3 C11-OU3-2</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -2886,7 +2886,7 @@
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>LCOS Signal 1 UID 33; STOP/APPROACH/CLEAR; lamp G; was S1-6 G/R/Y silk</t>
+          <t>LCOS Signal 1 UID 33; STOP/APPROACH/CLEAR; lamp G; was S1-6; sequential G/Y/R</t>
         </is>
       </c>
     </row>
@@ -2932,7 +2932,7 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>C11-OU3-1 C11-OU3-2 C11-OU3-3</t>
+          <t>C11-OU3-4 C11-OU3-6 C11-OU3-5</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -2957,7 +2957,7 @@
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>LCOS Signal 2 UID 34; STOP/APPROACH/CLEAR; lamp G; was S4-6 G/R/Y silk</t>
+          <t>LCOS Signal 2 UID 34; STOP/APPROACH/CLEAR; lamp G; was S4-6; sequential G/Y/R</t>
         </is>
       </c>
     </row>

--- a/cats/data/signals_asbuilt_abs_v2.xlsx
+++ b/cats/data/signals_asbuilt_abs_v2.xlsx
@@ -1280,7 +1280,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>C3</t>
+          <t>C4</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -1290,7 +1290,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>C3-OU2-1 C3-OU2-3 C3-OU2-2 C3-OU2-4 C3-OU2-6 C3-OU2-5</t>
+          <t>C4-OU2-1 C4-OU2-3 C4-OU2-2 C4-OU2-4 C4-OU2-6 C4-OU2-5</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -1355,7 +1355,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>C3</t>
+          <t>C4</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -1365,7 +1365,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>C3-OU2-7 C3-OU3-7 C3-OU2-8</t>
+          <t>C4-OU2-7 C4-OU3-7 C4-OU2-8</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1430,7 +1430,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>C3</t>
+          <t>C4</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -1440,7 +1440,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>C3-OU3-1 C3-OU3-3 C3-OU3-2 C3-OU3-4 C3-OU3-6 C3-OU3-5</t>
+          <t>C4-OU3-1 C4-OU3-3 C4-OU3-2 C4-OU3-4 C4-OU3-6 C4-OU3-5</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1505,7 +1505,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>C3</t>
+          <t>C4</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1515,7 +1515,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>C3-OU4-1 C3-OU4-3 C3-OU4-2</t>
+          <t>C4-OU4-1 C4-OU4-3 C4-OU4-2</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1580,7 +1580,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>C3</t>
+          <t>C4</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1590,7 +1590,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>C3-OU4-4 C3-OU4-6 C3-OU4-5</t>
+          <t>C4-OU4-4 C4-OU4-6 C4-OU4-5</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2140,7 +2140,7 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>LCOS Signal 1 UID 33; STOP/APPROACH/CLEAR; lamp G; was moved from OU1 with 24RA</t>
+          <t>LCOS Signal 1 UID 33; STOP/APPROACH/CLEAR; lamp G; was with 24RA cluster</t>
         </is>
       </c>
     </row>
@@ -2175,32 +2175,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>C2</t>
+          <t>C12</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>235 240</t>
+          <t>1232 1233</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>C2-OU3-1 C2-OU3-3 C2-OU3-2 C2-OU3-4 C2-OU3-6 C2-OU3-5</t>
+          <t>C12-OU2-1 C12-OU2-3 C12-OU2-2 C12-OU2-4 C12-OU2-6 C12-OU2-5</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>track/signalhead/235 track/signalhead/240</t>
+          <t>track/signalhead/1232 track/signalhead/1233</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>IF$shsm:hart-aar:SL-2-digicon(IH235)(IH240)</t>
+          <t>IF$shsm:hart-aar:SL-2-digicon(IH1232)(IH1233)</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -2215,7 +2215,7 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>LCOS Signal 3 UID 35; STOP/APPROACH/CLEAR; lamp G; was was S2-5/S2-3 mix</t>
+          <t>LCOS Signal 0 UID 32; STOP/APPROACH/CLEAR; lamp G; was was C2 235</t>
         </is>
       </c>
     </row>
@@ -2250,32 +2250,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>C2</t>
+          <t>C12</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>236</t>
+          <t>1234</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>C2-OU3-7 C2-OU4-7 C2-OU3-8</t>
+          <t>C12-OU2-7 C12-OU3-7 C12-OU2-8</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>track/signalhead/236</t>
+          <t>track/signalhead/1234</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>IF$shsm:AAR-1946:SL-1-low(IH236)</t>
+          <t>IF$shsm:AAR-1946:SL-1-low(IH1234)</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -2290,7 +2290,7 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>LCOS Signal 4 UID 36; STOP/APPROACH/CLEAR; lamp G; was G/Y with 34L; R spills to 34R OU4</t>
+          <t>LCOS Signal 2 UID 34; STOP/APPROACH/CLEAR; lamp G; was G/Y with 34L; R spills to 34R OU3</t>
         </is>
       </c>
     </row>
@@ -2325,32 +2325,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>C2</t>
+          <t>C12</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>237 241</t>
+          <t>1235 1236</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>C2-OU4-1 C2-OU4-3 C2-OU4-2 C2-OU4-4 C2-OU4-6 C2-OU4-5</t>
+          <t>C12-OU3-1 C12-OU3-3 C12-OU3-2 C12-OU3-4 C12-OU3-6 C12-OU3-5</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>track/signalhead/237 track/signalhead/241</t>
+          <t>track/signalhead/1235 track/signalhead/1236</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>IF$shsm:hart-aar:SL-2-digicon(IH237)(IH241)</t>
+          <t>IF$shsm:hart-aar:SL-2-digicon(IH1235)(IH1236)</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -2365,7 +2365,7 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>LCOS Signal 5 UID 37; STOP/APPROACH/CLEAR; lamp G; was was S4-6 G/R/Y</t>
+          <t>LCOS Signal 3 UID 35; STOP/APPROACH/CLEAR; lamp G; was was C2 237</t>
         </is>
       </c>
     </row>
@@ -2452,11 +2452,11 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Mast 40LA</t>
+          <t>Mast 36RB</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2465,12 +2465,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>(43,6) RIGHT</t>
+          <t>(37,7) LEFT</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Switch 39</t>
+          <t>Switch 35</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -2485,37 +2485,37 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>142</t>
+          <t>132 133</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>C1-OU3-7 C1-OU2-7 C1-OU3-8</t>
+          <t>C1-OU3-1 C1-OU3-3 C1-OU3-2 C1-OU3-4 C1-OU3-6 C1-OU3-5</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>track/signalhead/142</t>
+          <t>track/signalhead/132 track/signalhead/133</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>IF$shsm:AAR-1946:SL-1-low(IH142)</t>
+          <t>IF$shsm:hart-aar:SL-2-digicon(IH132)(IH133)</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>single</t>
+          <t>double</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>AAR-1946 SL-1-low (3-pin STOP/APPROACH/CLEAR)</t>
+          <t>hart-aar SL-2-digicon (two 3-pin STOP/APPROACH/CLEAR discs)</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>LCOS Signal 10 UID 42; STOP/APPROACH/CLEAR; lamp G; was G/Y with 40LB; R spills to 36RA OU2</t>
+          <t>LCOS Signal 0 UID 32; STOP/APPROACH/CLEAR; lamp G; was was C11 1132</t>
         </is>
       </c>
     </row>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Mast 40LB</t>
+          <t>Mast 38LB</t>
         </is>
       </c>
       <c r="C19" t="n">
@@ -2540,12 +2540,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>(43,5) RIGHT</t>
+          <t>(43,8) RIGHT</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Switch 39</t>
+          <t>Switch 37</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -2560,22 +2560,22 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>132 133</t>
+          <t>139 140</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>C1-OU3-1 C1-OU3-3 C1-OU3-2 C1-OU3-4 C1-OU3-6 C1-OU3-5</t>
+          <t>C1-OU4-1 C1-OU4-3 C1-OU4-2 C1-OU4-4 C1-OU4-6 C1-OU4-5</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>track/signalhead/132 track/signalhead/133</t>
+          <t>track/signalhead/139 track/signalhead/140</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>IF$shsm:hart-aar:SL-2-digicon(IH132)(IH133)</t>
+          <t>IF$shsm:hart-aar:SL-2-digicon(IH139)(IH140)</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -2590,7 +2590,7 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>LCOS Signal 0 UID 32; STOP/APPROACH/CLEAR; lamp G; was S1-1 G/Y/R</t>
+          <t>LCOS Signal 7 UID 39; STOP/APPROACH/CLEAR; lamp G; was S1-3 G/Y/R</t>
         </is>
       </c>
     </row>
@@ -2640,7 +2640,7 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>C1-OU4-7 C1-OU2-8 C1-OU4-8</t>
+          <t>C1-OU4-7 C1-OU2-7 C1-OU4-8</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -2677,7 +2677,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Mast 38LB</t>
+          <t>Mast 40LB</t>
         </is>
       </c>
       <c r="C21" t="n">
@@ -2690,42 +2690,42 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>(43,8) RIGHT</t>
+          <t>(43,5) RIGHT</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Switch 37</t>
+          <t>Switch 39</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>C1</t>
+          <t>C11</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>139 140</t>
+          <t>1132 1135</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>C1-OU4-1 C1-OU4-3 C1-OU4-2 C1-OU4-4 C1-OU4-6 C1-OU4-5</t>
+          <t>C11-OU2-1 C11-OU2-3 C11-OU2-2 C11-OU2-4 C11-OU2-6 C11-OU2-5</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>track/signalhead/139 track/signalhead/140</t>
+          <t>track/signalhead/1132 track/signalhead/1135</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>IF$shsm:hart-aar:SL-2-digicon(IH139)(IH140)</t>
+          <t>IF$shsm:hart-aar:SL-2-digicon(IH1132)(IH1135)</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -2740,7 +2740,7 @@
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>LCOS Signal 7 UID 39; STOP/APPROACH/CLEAR; lamp G; was S1-3 G/Y/R</t>
+          <t>LCOS Signal 0 UID 32; STOP/APPROACH/CLEAR; lamp G; was was C1 132</t>
         </is>
       </c>
     </row>
@@ -2752,11 +2752,11 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Mast 36RB</t>
+          <t>Mast 40LA</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2765,12 +2765,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>(37,7) LEFT</t>
+          <t>(43,6) RIGHT</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Switch 35</t>
+          <t>Switch 39</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -2785,37 +2785,37 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>1132 1135</t>
+          <t>1136</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>C11-OU2-1 C11-OU2-3 C11-OU2-2 C11-OU2-4 C11-OU2-6 C11-OU2-5</t>
+          <t>C11-OU2-7 C11-OU3-7 C11-OU2-8</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>track/signalhead/1132 track/signalhead/1135</t>
+          <t>track/signalhead/1136</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>IF$shsm:hart-aar:SL-2-digicon(IH1132)(IH1135)</t>
+          <t>IF$shsm:AAR-1946:SL-1-low(IH1136)</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>double</t>
+          <t>single</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>hart-aar SL-2-digicon (two 3-pin STOP/APPROACH/CLEAR discs)</t>
+          <t>AAR-1946 SL-1-low (3-pin STOP/APPROACH/CLEAR)</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>LCOS Signal 0 UID 32; STOP/APPROACH/CLEAR; lamp G; was S1-5; sequential G/Y/R</t>
+          <t>LCOS Signal 4 UID 36; STOP/APPROACH/CLEAR; lamp G; was G/Y with 40LB; R spills to balloon OU3</t>
         </is>
       </c>
     </row>

--- a/cats/data/signals_asbuilt_abs_v2.xlsx
+++ b/cats/data/signals_asbuilt_abs_v2.xlsx
@@ -1365,7 +1365,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>C4-OU2-7 C4-OU3-7 C4-OU2-8</t>
+          <t>C4-OU2-7 C4-OU3-7 C4-OU3-8</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1390,7 +1390,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>LCOS Signal 2 UID 34; STOP/APPROACH/CLEAR; lamp G; was G/Y on Plane OU2; R spills to 2L OU3</t>
+          <t>LCOS Signal 2 UID 34; STOP/APPROACH/CLEAR; lamp G; was G on Plane OU2; Y/R on 2L OU3 (OU2-8 is BS cal)</t>
         </is>
       </c>
     </row>
@@ -2040,7 +2040,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>C2-OU1-7 C2-OU2-7 C2-OU1-8</t>
+          <t>C2-OU1-7 C2-OU2-7 C2-OU3-8</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -2065,7 +2065,7 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>LCOS Signal 2 UID 34; STOP/APPROACH/CLEAR; lamp G; was G/Y with 24RA; R spills to 24L OU2</t>
+          <t>LCOS Signal 2 UID 34; STOP/APPROACH/CLEAR; lamp G; was G with 24RA; Y on OU3 (OU1-8 is BS cal); R with 24L</t>
         </is>
       </c>
     </row>
@@ -2265,7 +2265,7 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>C12-OU2-7 C12-OU3-7 C12-OU2-8</t>
+          <t>C12-OU2-7 C12-OU3-7 C12-OU3-8</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -2290,7 +2290,7 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>LCOS Signal 2 UID 34; STOP/APPROACH/CLEAR; lamp G; was G/Y with 34L; R spills to 34R OU3</t>
+          <t>LCOS Signal 2 UID 34; STOP/APPROACH/CLEAR; lamp G; was G with 34L; Y/R on 34R OU3 (OU2-8 is BS cal)</t>
         </is>
       </c>
     </row>
@@ -2790,7 +2790,7 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>C11-OU2-7 C11-OU3-7 C11-OU2-8</t>
+          <t>C11-OU2-7 C11-OU3-7 C11-OU3-8</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -2815,7 +2815,7 @@
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>LCOS Signal 4 UID 36; STOP/APPROACH/CLEAR; lamp G; was G/Y with 40LB; R spills to balloon OU3</t>
+          <t>LCOS Signal 4 UID 36; STOP/APPROACH/CLEAR; lamp G; was G with 40LB; Y/R on balloon OU3 (OU2-8 is BS cal)</t>
         </is>
       </c>
     </row>

--- a/cats/data/signals_asbuilt_abs_v2.xlsx
+++ b/cats/data/signals_asbuilt_abs_v2.xlsx
@@ -2040,7 +2040,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>C2-OU1-7 C2-OU2-7 C2-OU3-8</t>
+          <t>C2-OU3-6 C2-OU3-8 C2-OU3-7</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -2065,7 +2065,7 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>LCOS Signal 2 UID 34; STOP/APPROACH/CLEAR; lamp G; was G with 24RA; Y on OU3 (OU1-8 is BS cal); R with 24L</t>
+          <t>LCOS Signal 2 UID 34; STOP/APPROACH/CLEAR; lamp G; was whole dwarf on leftover OU3 (OU1-8 is BS cal)</t>
         </is>
       </c>
     </row>
@@ -2640,7 +2640,7 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>C1-OU4-7 C1-OU2-7 C1-OU4-8</t>
+          <t>C1-OU3-7 C1-OU2-7 C1-OU3-8</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -2665,7 +2665,7 @@
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>LCOS Signal 11 UID 43; STOP/APPROACH/CLEAR; lamp G; was G/Y with 38LB; R spills to 36RA OU2</t>
+          <t>LCOS Signal 11 UID 43; STOP/APPROACH/CLEAR; lamp G; was leftover trio on 36 boards; 38LB keeps OU4</t>
         </is>
       </c>
     </row>

--- a/cats/data/signals_asbuilt_abs_v2.xlsx
+++ b/cats/data/signals_asbuilt_abs_v2.xlsx
@@ -2790,7 +2790,7 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>C11-OU2-7 C11-OU3-7 C11-OU3-8</t>
+          <t>C11-OU3-1 C11-OU3-3 C11-OU3-2</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -2815,7 +2815,7 @@
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>LCOS Signal 4 UID 36; STOP/APPROACH/CLEAR; lamp G; was G with 40LB; Y/R on balloon OU3 (OU2-8 is BS cal)</t>
+          <t>LCOS Signal 4 UID 36; STOP/APPROACH/CLEAR; lamp G; was whole dwarf on OU3; 2035/2036 can sit apart</t>
         </is>
       </c>
     </row>
@@ -2861,7 +2861,7 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>C11-OU3-1 C11-OU3-3 C11-OU3-2</t>
+          <t>C11-OU3-4 C11-OU3-6 C11-OU3-5</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -2886,7 +2886,7 @@
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>LCOS Signal 1 UID 33; STOP/APPROACH/CLEAR; lamp G; was S1-6; sequential G/Y/R</t>
+          <t>LCOS Signal 1 UID 33; STOP/APPROACH/CLEAR; lamp G; was balloon; sequential G/Y/R</t>
         </is>
       </c>
     </row>
@@ -2932,7 +2932,7 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>C11-OU3-4 C11-OU3-6 C11-OU3-5</t>
+          <t>C11-OU3-7 C11-OU2-7 C11-OU3-8</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -2957,7 +2957,7 @@
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>LCOS Signal 2 UID 34; STOP/APPROACH/CLEAR; lamp G; was S4-6; sequential G/Y/R</t>
+          <t>LCOS Signal 2 UID 34; STOP/APPROACH/CLEAR; lamp G; was leftover trio (OU2-8 is BS cal)</t>
         </is>
       </c>
     </row>

--- a/cats/data/signals_asbuilt_abs_v2.xlsx
+++ b/cats/data/signals_asbuilt_abs_v2.xlsx
@@ -1290,7 +1290,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>C4-OU2-1 C4-OU2-3 C4-OU2-2 C4-OU2-4 C4-OU2-6 C4-OU2-5</t>
+          <t>C4-OU2-3 C4-OU2-1 C4-OU2-2 C4-OU2-6 C4-OU2-4 C4-OU2-5</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -1300,7 +1300,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>IF$shsm:hart-aar:SL-2-digicon(IH432)(IH433)</t>
+          <t>IF$shsm:C&amp;O-1980:CO-33-hi(IH432)(IH433)</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -1310,12 +1310,12 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>hart-aar SL-2-digicon (two 3-pin STOP/APPROACH/CLEAR discs)</t>
+          <t>hart C&amp;O-1980 (two 3-pin STOP/APPROACH/CLEAR discs)</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>LCOS Signal 0 UID 32; STOP/APPROACH/CLEAR; lamp G; was S3-6 G/Y/R</t>
+          <t>LCOS Signal 0 UID 32; STOP/APPROACH/CLEAR; lamp G; was S3-6 R/Y/G</t>
         </is>
       </c>
     </row>
@@ -1365,7 +1365,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>C4-OU2-7 C4-OU3-7 C4-OU3-8</t>
+          <t>C4-OU3-7 C4-OU2-7 C4-OU3-8</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1375,7 +1375,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>IF$shsm:AAR-1946:SL-1-low(IH434)</t>
+          <t>IF$shsm:C&amp;O-1980:CO-3-dwarf(IH434)</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -1385,12 +1385,12 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>AAR-1946 SL-1-low (3-pin STOP/APPROACH/CLEAR)</t>
+          <t>C&amp;O-1980 CO-3-dwarf (3-pin STOP/APPROACH/CLEAR)</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>LCOS Signal 2 UID 34; STOP/APPROACH/CLEAR; lamp G; was G on Plane OU2; Y/R on 2L OU3 (OU2-8 is BS cal)</t>
+          <t>LCOS Signal 2 UID 34; STOP/APPROACH/CLEAR; lamp G; was R on Plane OU2; Y/G on 2L OU3 (OU2-8 is BS cal)</t>
         </is>
       </c>
     </row>
@@ -1440,7 +1440,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>C4-OU3-1 C4-OU3-3 C4-OU3-2 C4-OU3-4 C4-OU3-6 C4-OU3-5</t>
+          <t>C4-OU3-3 C4-OU3-1 C4-OU3-2 C4-OU3-6 C4-OU3-4 C4-OU3-5</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1450,7 +1450,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>IF$shsm:hart-aar:SL-2-digicon(IH438)(IH439)</t>
+          <t>IF$shsm:C&amp;O-1980:CO-33-hi(IH438)(IH439)</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -1460,12 +1460,12 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>hart-aar SL-2-digicon (two 3-pin STOP/APPROACH/CLEAR discs)</t>
+          <t>hart C&amp;O-1980 (two 3-pin STOP/APPROACH/CLEAR discs)</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>LCOS Signal 6 UID 38; STOP/APPROACH/CLEAR; lamp G; was S3-8 G/Y/R</t>
+          <t>LCOS Signal 6 UID 38; STOP/APPROACH/CLEAR; lamp G; was S3-8 R/Y/G</t>
         </is>
       </c>
     </row>
@@ -1515,7 +1515,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>C4-OU4-1 C4-OU4-3 C4-OU4-2</t>
+          <t>C4-OU4-3 C4-OU4-1 C4-OU4-2</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1525,7 +1525,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>IF$shsm:AAR-1946:SL-1-low(IH436)</t>
+          <t>IF$shsm:C&amp;O-1980:CO-3-dwarf(IH436)</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -1535,7 +1535,7 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>AAR-1946 SL-1-low (3-pin STOP/APPROACH/CLEAR)</t>
+          <t>C&amp;O-1980 CO-3-dwarf (3-pin STOP/APPROACH/CLEAR)</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -1590,7 +1590,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>C4-OU4-4 C4-OU4-6 C4-OU4-5</t>
+          <t>C4-OU4-6 C4-OU4-4 C4-OU4-5</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1600,7 +1600,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>IF$shsm:AAR-1946:SL-1-low(IH437)</t>
+          <t>IF$shsm:C&amp;O-1980:CO-3-dwarf(IH437)</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -1610,7 +1610,7 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>AAR-1946 SL-1-low (3-pin STOP/APPROACH/CLEAR)</t>
+          <t>C&amp;O-1980 CO-3-dwarf (3-pin STOP/APPROACH/CLEAR)</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -1665,7 +1665,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>C13-OU1-1 C13-OU1-3 C13-OU1-2 C13-OU1-4 C13-OU1-6 C13-OU1-5</t>
+          <t>C13-OU1-3 C13-OU1-1 C13-OU1-2 C13-OU1-6 C13-OU1-4 C13-OU1-5</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1675,7 +1675,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>IF$shsm:hart-aar:SL-2-digicon(IH1332)(IH1333)</t>
+          <t>IF$shsm:C&amp;O-1980:CO-33-hi(IH1332)(IH1333)</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -1685,12 +1685,12 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>hart-aar SL-2-digicon (two 3-pin STOP/APPROACH/CLEAR discs)</t>
+          <t>hart C&amp;O-1980 (two 3-pin STOP/APPROACH/CLEAR discs)</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>LCOS Signal 0 UID 32; STOP/APPROACH/CLEAR; lamp G; was S3-10 G/Y/R</t>
+          <t>LCOS Signal 0 UID 32; STOP/APPROACH/CLEAR; lamp G; was S3-10 R/Y/G</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>C13-OU4-1 C13-OU4-3 C13-OU4-2 C13-OU4-4 C13-OU4-6 C13-OU4-5</t>
+          <t>C13-OU4-3 C13-OU4-1 C13-OU4-2 C13-OU4-6 C13-OU4-4 C13-OU4-5</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -1750,7 +1750,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>IF$shsm:hart-aar:SL-2-digicon(IH1335)(IH1336)</t>
+          <t>IF$shsm:C&amp;O-1980:CO-33-hi(IH1335)(IH1336)</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -1760,12 +1760,12 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>hart-aar SL-2-digicon (two 3-pin STOP/APPROACH/CLEAR discs)</t>
+          <t>hart C&amp;O-1980 (two 3-pin STOP/APPROACH/CLEAR discs)</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>LCOS Signal 3 UID 35; STOP/APPROACH/CLEAR; lamp G; was S3-12; sequential G/Y/R</t>
+          <t>LCOS Signal 3 UID 35; STOP/APPROACH/CLEAR; lamp G; was S3-12; sequential R/Y/G</t>
         </is>
       </c>
     </row>
@@ -1815,7 +1815,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>C13-OU2-1 C13-OU2-3 C13-OU2-2 C13-OU2-4 C13-OU2-6 C13-OU2-5</t>
+          <t>C13-OU2-3 C13-OU2-1 C13-OU2-2 C13-OU2-6 C13-OU2-4 C13-OU2-5</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -1825,7 +1825,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>IF$shsm:hart-aar:SL-2-digicon(IH1337)(IH1338)</t>
+          <t>IF$shsm:C&amp;O-1980:CO-33-hi(IH1337)(IH1338)</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -1835,12 +1835,12 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>hart-aar SL-2-digicon (two 3-pin STOP/APPROACH/CLEAR discs)</t>
+          <t>hart C&amp;O-1980 (two 3-pin STOP/APPROACH/CLEAR discs)</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>LCOS Signal 5 UID 37; STOP/APPROACH/CLEAR; lamp G; was S3-5 G/Y/R</t>
+          <t>LCOS Signal 5 UID 37; STOP/APPROACH/CLEAR; lamp G; was S3-5 R/Y/G</t>
         </is>
       </c>
     </row>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>C13-OU2-7 C13-OU4-7 C13-OU2-8</t>
+          <t>C13-OU4-7 C13-OU2-7 C13-OU2-8</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1900,7 +1900,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>IF$shsm:AAR-1946:SL-1-low(IH1334)</t>
+          <t>IF$shsm:C&amp;O-1980:CO-3-dwarf(IH1334)</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>AAR-1946 SL-1-low (3-pin STOP/APPROACH/CLEAR)</t>
+          <t>C&amp;O-1980 CO-3-dwarf (3-pin STOP/APPROACH/CLEAR)</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>LCOS Signal 2 UID 34; STOP/APPROACH/CLEAR; lamp G; was G/Y with 8LA; R spills to 8RB OU4</t>
+          <t>LCOS Signal 2 UID 34; STOP/APPROACH/CLEAR; lamp G; was R/Y with 8LA; G spills to 8RB OU4</t>
         </is>
       </c>
     </row>
@@ -1965,7 +1965,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>C2-OU1-1 C2-OU1-3 C2-OU1-2 C2-OU1-4 C2-OU1-6 C2-OU1-5</t>
+          <t>C2-OU1-3 C2-OU1-1 C2-OU1-2 C2-OU1-6 C2-OU1-4 C2-OU1-5</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1975,7 +1975,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>IF$shsm:hart-aar:SL-2-digicon(IH232)(IH238)</t>
+          <t>IF$shsm:C&amp;O-1980:CO-33-hi(IH232)(IH238)</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1985,7 +1985,7 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>hart-aar SL-2-digicon (two 3-pin STOP/APPROACH/CLEAR discs)</t>
+          <t>hart C&amp;O-1980 (two 3-pin STOP/APPROACH/CLEAR discs)</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -2040,7 +2040,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>C2-OU3-6 C2-OU3-8 C2-OU3-7</t>
+          <t>C2-OU3-8 C2-OU3-6 C2-OU3-7</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -2050,7 +2050,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>IF$shsm:AAR-1946:SL-1-low(IH234)</t>
+          <t>IF$shsm:C&amp;O-1980:CO-3-dwarf(IH234)</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -2060,7 +2060,7 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>AAR-1946 SL-1-low (3-pin STOP/APPROACH/CLEAR)</t>
+          <t>C&amp;O-1980 CO-3-dwarf (3-pin STOP/APPROACH/CLEAR)</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>C2-OU2-1 C2-OU2-3 C2-OU2-2 C2-OU2-4 C2-OU2-6 C2-OU2-5</t>
+          <t>C2-OU2-3 C2-OU2-1 C2-OU2-2 C2-OU2-6 C2-OU2-4 C2-OU2-5</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -2125,7 +2125,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>IF$shsm:hart-aar:SL-2-digicon(IH233)(IH239)</t>
+          <t>IF$shsm:C&amp;O-1980:CO-33-hi(IH233)(IH239)</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -2135,7 +2135,7 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>hart-aar SL-2-digicon (two 3-pin STOP/APPROACH/CLEAR discs)</t>
+          <t>hart C&amp;O-1980 (two 3-pin STOP/APPROACH/CLEAR discs)</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
@@ -2190,7 +2190,7 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>C12-OU2-1 C12-OU2-3 C12-OU2-2 C12-OU2-4 C12-OU2-6 C12-OU2-5</t>
+          <t>C12-OU2-3 C12-OU2-1 C12-OU2-2 C12-OU2-6 C12-OU2-4 C12-OU2-5</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -2200,7 +2200,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>IF$shsm:hart-aar:SL-2-digicon(IH1232)(IH1233)</t>
+          <t>IF$shsm:C&amp;O-1980:CO-33-hi(IH1232)(IH1233)</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -2210,7 +2210,7 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>hart-aar SL-2-digicon (two 3-pin STOP/APPROACH/CLEAR discs)</t>
+          <t>hart C&amp;O-1980 (two 3-pin STOP/APPROACH/CLEAR discs)</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
@@ -2265,7 +2265,7 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>C12-OU2-7 C12-OU3-7 C12-OU3-8</t>
+          <t>C12-OU3-7 C12-OU2-7 C12-OU3-8</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -2275,7 +2275,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>IF$shsm:AAR-1946:SL-1-low(IH1234)</t>
+          <t>IF$shsm:C&amp;O-1980:CO-3-dwarf(IH1234)</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -2285,12 +2285,12 @@
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>AAR-1946 SL-1-low (3-pin STOP/APPROACH/CLEAR)</t>
+          <t>C&amp;O-1980 CO-3-dwarf (3-pin STOP/APPROACH/CLEAR)</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>LCOS Signal 2 UID 34; STOP/APPROACH/CLEAR; lamp G; was G with 34L; Y/R on 34R OU3 (OU2-8 is BS cal)</t>
+          <t>LCOS Signal 2 UID 34; STOP/APPROACH/CLEAR; lamp G; was R with 34L; Y/G on 34R OU3 (OU2-8 is BS cal)</t>
         </is>
       </c>
     </row>
@@ -2340,7 +2340,7 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>C12-OU3-1 C12-OU3-3 C12-OU3-2 C12-OU3-4 C12-OU3-6 C12-OU3-5</t>
+          <t>C12-OU3-3 C12-OU3-1 C12-OU3-2 C12-OU3-6 C12-OU3-4 C12-OU3-5</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -2350,7 +2350,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>IF$shsm:hart-aar:SL-2-digicon(IH1235)(IH1236)</t>
+          <t>IF$shsm:C&amp;O-1980:CO-33-hi(IH1235)(IH1236)</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -2360,7 +2360,7 @@
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>hart-aar SL-2-digicon (two 3-pin STOP/APPROACH/CLEAR discs)</t>
+          <t>hart C&amp;O-1980 (two 3-pin STOP/APPROACH/CLEAR discs)</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
@@ -2415,7 +2415,7 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>C1-OU2-1 C1-OU2-3 C1-OU2-2 C1-OU2-4 C1-OU2-6 C1-OU2-5</t>
+          <t>C1-OU2-3 C1-OU2-1 C1-OU2-2 C1-OU2-6 C1-OU2-4 C1-OU2-5</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -2425,7 +2425,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>IF$shsm:hart-aar:SL-2-digicon(IH135)(IH136)</t>
+          <t>IF$shsm:C&amp;O-1980:CO-33-hi(IH135)(IH136)</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -2435,12 +2435,12 @@
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>hart-aar SL-2-digicon (two 3-pin STOP/APPROACH/CLEAR discs)</t>
+          <t>hart C&amp;O-1980 (two 3-pin STOP/APPROACH/CLEAR discs)</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>LCOS Signal 3 UID 35; STOP/APPROACH/CLEAR; lamp G; was S1-2 G/Y/R</t>
+          <t>LCOS Signal 3 UID 35; STOP/APPROACH/CLEAR; lamp G; was S1-2 R/Y/G</t>
         </is>
       </c>
     </row>
@@ -2490,7 +2490,7 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>C1-OU3-1 C1-OU3-3 C1-OU3-2 C1-OU3-4 C1-OU3-6 C1-OU3-5</t>
+          <t>C1-OU3-3 C1-OU3-1 C1-OU3-2 C1-OU3-6 C1-OU3-4 C1-OU3-5</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -2500,7 +2500,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>IF$shsm:hart-aar:SL-2-digicon(IH132)(IH133)</t>
+          <t>IF$shsm:C&amp;O-1980:CO-33-hi(IH132)(IH133)</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -2510,7 +2510,7 @@
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>hart-aar SL-2-digicon (two 3-pin STOP/APPROACH/CLEAR discs)</t>
+          <t>hart C&amp;O-1980 (two 3-pin STOP/APPROACH/CLEAR discs)</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>C1-OU4-1 C1-OU4-3 C1-OU4-2 C1-OU4-4 C1-OU4-6 C1-OU4-5</t>
+          <t>C1-OU4-3 C1-OU4-1 C1-OU4-2 C1-OU4-6 C1-OU4-4 C1-OU4-5</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -2575,7 +2575,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>IF$shsm:hart-aar:SL-2-digicon(IH139)(IH140)</t>
+          <t>IF$shsm:C&amp;O-1980:CO-33-hi(IH139)(IH140)</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -2585,12 +2585,12 @@
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>hart-aar SL-2-digicon (two 3-pin STOP/APPROACH/CLEAR discs)</t>
+          <t>hart C&amp;O-1980 (two 3-pin STOP/APPROACH/CLEAR discs)</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>LCOS Signal 7 UID 39; STOP/APPROACH/CLEAR; lamp G; was S1-3 G/Y/R</t>
+          <t>LCOS Signal 7 UID 39; STOP/APPROACH/CLEAR; lamp G; was S1-3 R/Y/G</t>
         </is>
       </c>
     </row>
@@ -2640,7 +2640,7 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>C1-OU3-7 C1-OU2-7 C1-OU3-8</t>
+          <t>C1-OU2-7 C1-OU3-7 C1-OU3-8</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -2650,7 +2650,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>IF$shsm:AAR-1946:SL-1-low(IH143)</t>
+          <t>IF$shsm:C&amp;O-1980:CO-3-dwarf(IH143)</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -2660,7 +2660,7 @@
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>AAR-1946 SL-1-low (3-pin STOP/APPROACH/CLEAR)</t>
+          <t>C&amp;O-1980 CO-3-dwarf (3-pin STOP/APPROACH/CLEAR)</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
@@ -2715,7 +2715,7 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>C11-OU2-1 C11-OU2-3 C11-OU2-2 C11-OU2-4 C11-OU2-6 C11-OU2-5</t>
+          <t>C11-OU2-3 C11-OU2-1 C11-OU2-2 C11-OU2-6 C11-OU2-4 C11-OU2-5</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -2725,7 +2725,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>IF$shsm:hart-aar:SL-2-digicon(IH1132)(IH1135)</t>
+          <t>IF$shsm:C&amp;O-1980:CO-33-hi(IH1132)(IH1135)</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -2735,7 +2735,7 @@
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>hart-aar SL-2-digicon (two 3-pin STOP/APPROACH/CLEAR discs)</t>
+          <t>hart C&amp;O-1980 (two 3-pin STOP/APPROACH/CLEAR discs)</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
@@ -2790,7 +2790,7 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>C11-OU3-1 C11-OU3-3 C11-OU3-2</t>
+          <t>C11-OU3-3 C11-OU3-1 C11-OU3-2</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -2800,7 +2800,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>IF$shsm:AAR-1946:SL-1-low(IH1136)</t>
+          <t>IF$shsm:C&amp;O-1980:CO-3-dwarf(IH1136)</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>AAR-1946 SL-1-low (3-pin STOP/APPROACH/CLEAR)</t>
+          <t>C&amp;O-1980 CO-3-dwarf (3-pin STOP/APPROACH/CLEAR)</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
@@ -2861,7 +2861,7 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>C11-OU3-4 C11-OU3-6 C11-OU3-5</t>
+          <t>C11-OU3-6 C11-OU3-4 C11-OU3-5</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -2871,7 +2871,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>IF$shsm:AAR-1946:SL-1-low(IH1133)</t>
+          <t>IF$shsm:C&amp;O-1980:CO-3-dwarf(IH1133)</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -2881,12 +2881,12 @@
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>AAR-1946 SL-1-low (3-pin STOP/APPROACH/CLEAR)</t>
+          <t>C&amp;O-1980 CO-3-dwarf (3-pin STOP/APPROACH/CLEAR)</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>LCOS Signal 1 UID 33; STOP/APPROACH/CLEAR; lamp G; was balloon; sequential G/Y/R</t>
+          <t>LCOS Signal 1 UID 33; STOP/APPROACH/CLEAR; lamp G; was balloon; sequential R/Y/G</t>
         </is>
       </c>
     </row>
@@ -2932,7 +2932,7 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>C11-OU3-7 C11-OU2-7 C11-OU3-8</t>
+          <t>C11-OU2-7 C11-OU3-7 C11-OU3-8</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -2942,7 +2942,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>IF$shsm:AAR-1946:SL-1-low(IH1134)</t>
+          <t>IF$shsm:C&amp;O-1980:CO-3-dwarf(IH1134)</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -2952,7 +2952,7 @@
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>AAR-1946 SL-1-low (3-pin STOP/APPROACH/CLEAR)</t>
+          <t>C&amp;O-1980 CO-3-dwarf (3-pin STOP/APPROACH/CLEAR)</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
@@ -9469,7 +9469,7 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>K-1 dwarf (SL-1-low). SW115 Closed = K-1. Dest 111L when 113 Normal.</t>
+          <t>K-1 dwarf (CO-3-dwarf). SW115 Closed = K-1. Dest 111L when 113 Normal.</t>
         </is>
       </c>
     </row>
@@ -9551,7 +9551,7 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>K-1 dwarf (SL-1-low). SW115 Closed = K-1. Dest 111L when 113 Normal.</t>
+          <t>K-1 dwarf (CO-3-dwarf). SW115 Closed = K-1. Dest 111L when 113 Normal.</t>
         </is>
       </c>
     </row>
@@ -9633,7 +9633,7 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>K-1 dwarf (SL-1-low). SW115 Closed = K-1. Dest 111L when 113 Normal.</t>
+          <t>K-1 dwarf (CO-3-dwarf). SW115 Closed = K-1. Dest 111L when 113 Normal.</t>
         </is>
       </c>
     </row>
@@ -9951,7 +9951,7 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>K-2 dwarf (SL-1-low). SW114 Closed = K-2. Dest 111L when 113 Normal.</t>
+          <t>K-2 dwarf (CO-3-dwarf). SW114 Closed = K-2. Dest 111L when 113 Normal.</t>
         </is>
       </c>
     </row>
@@ -10033,7 +10033,7 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>K-2 dwarf (SL-1-low). SW114 Closed = K-2. Dest 111L when 113 Normal.</t>
+          <t>K-2 dwarf (CO-3-dwarf). SW114 Closed = K-2. Dest 111L when 113 Normal.</t>
         </is>
       </c>
     </row>
@@ -10115,7 +10115,7 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>K-2 dwarf (SL-1-low). SW114 Closed = K-2. Dest 111L when 113 Normal.</t>
+          <t>K-2 dwarf (CO-3-dwarf). SW114 Closed = K-2. Dest 111L when 113 Normal.</t>
         </is>
       </c>
     </row>
@@ -10428,7 +10428,7 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>Balloon connector (SL-1-low). A48 east ends join: 120R/IH134 on McKeesport track protects Rocks / OS 115. SW114 Thrown = McKeesport.</t>
+          <t>Balloon connector (CO-3-dwarf). A48 east ends join: 120R/IH134 on McKeesport track protects Rocks / OS 115. SW114 Thrown = McKeesport.</t>
         </is>
       </c>
     </row>
@@ -10505,7 +10505,7 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>Balloon connector (SL-1-low). A48 east ends join: 120R/IH134 on McKeesport track protects Rocks / OS 115. SW114 Thrown = McKeesport.</t>
+          <t>Balloon connector (CO-3-dwarf). A48 east ends join: 120R/IH134 on McKeesport track protects Rocks / OS 115. SW114 Thrown = McKeesport.</t>
         </is>
       </c>
     </row>
@@ -10582,7 +10582,7 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>Balloon connector (SL-1-low). A48 east ends join: 120R/IH134 on McKeesport track protects Rocks / OS 115. SW114 Thrown = McKeesport.</t>
+          <t>Balloon connector (CO-3-dwarf). A48 east ends join: 120R/IH134 on McKeesport track protects Rocks / OS 115. SW114 Thrown = McKeesport.</t>
         </is>
       </c>
     </row>
@@ -10654,7 +10654,7 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>Balloon connector (SL-1-low). 120L/IH141 on Rocks track protects McKeesport / OS 114. SML also Stop if McKees Rocks occupied. SW115 Thrown = Rocks.</t>
+          <t>Balloon connector (CO-3-dwarf). 120L/IH141 on Rocks track protects McKeesport / OS 114. SML also Stop if McKees Rocks occupied. SW115 Thrown = Rocks.</t>
         </is>
       </c>
     </row>
@@ -10731,7 +10731,7 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>Balloon connector (SL-1-low). 120L/IH141 on Rocks track protects McKeesport / OS 114. SML also Stop if McKees Rocks occupied. SW115 Thrown = Rocks.</t>
+          <t>Balloon connector (CO-3-dwarf). 120L/IH141 on Rocks track protects McKeesport / OS 114. SML also Stop if McKees Rocks occupied. SW115 Thrown = Rocks.</t>
         </is>
       </c>
     </row>
@@ -10808,7 +10808,7 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>Balloon connector (SL-1-low). 120L/IH141 on Rocks track protects McKeesport / OS 114. SML also Stop if McKees Rocks occupied. SW115 Thrown = Rocks.</t>
+          <t>Balloon connector (CO-3-dwarf). 120L/IH141 on Rocks track protects McKeesport / OS 114. SML also Stop if McKees Rocks occupied. SW115 Thrown = Rocks.</t>
         </is>
       </c>
     </row>
@@ -16648,7 +16648,7 @@
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>K-1 dwarf (SL-1-low). SW115 Closed = K-1. Dest 111L when 113 Normal.</t>
+          <t>K-1 dwarf (CO-3-dwarf). SW115 Closed = K-1. Dest 111L when 113 Normal.</t>
         </is>
       </c>
     </row>
@@ -16730,7 +16730,7 @@
       </c>
       <c r="Y68" t="inlineStr">
         <is>
-          <t>K-1 dwarf (SL-1-low). SW115 Closed = K-1. Dest 111L when 113 Normal.</t>
+          <t>K-1 dwarf (CO-3-dwarf). SW115 Closed = K-1. Dest 111L when 113 Normal.</t>
         </is>
       </c>
     </row>
@@ -16812,7 +16812,7 @@
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>K-1 dwarf (SL-1-low). SW115 Closed = K-1. Dest 111L when 113 Normal.</t>
+          <t>K-1 dwarf (CO-3-dwarf). SW115 Closed = K-1. Dest 111L when 113 Normal.</t>
         </is>
       </c>
     </row>
@@ -17130,7 +17130,7 @@
       </c>
       <c r="Y73" t="inlineStr">
         <is>
-          <t>K-2 dwarf (SL-1-low). SW114 Closed = K-2. Dest 111L when 113 Normal.</t>
+          <t>K-2 dwarf (CO-3-dwarf). SW114 Closed = K-2. Dest 111L when 113 Normal.</t>
         </is>
       </c>
     </row>
@@ -17212,7 +17212,7 @@
       </c>
       <c r="Y74" t="inlineStr">
         <is>
-          <t>K-2 dwarf (SL-1-low). SW114 Closed = K-2. Dest 111L when 113 Normal.</t>
+          <t>K-2 dwarf (CO-3-dwarf). SW114 Closed = K-2. Dest 111L when 113 Normal.</t>
         </is>
       </c>
     </row>
@@ -17294,7 +17294,7 @@
       </c>
       <c r="Y75" t="inlineStr">
         <is>
-          <t>K-2 dwarf (SL-1-low). SW114 Closed = K-2. Dest 111L when 113 Normal.</t>
+          <t>K-2 dwarf (CO-3-dwarf). SW114 Closed = K-2. Dest 111L when 113 Normal.</t>
         </is>
       </c>
     </row>
@@ -17607,7 +17607,7 @@
       </c>
       <c r="Y79" t="inlineStr">
         <is>
-          <t>Balloon connector (SL-1-low). A48 east ends join: 120R/IH134 on McKeesport track protects Rocks / OS 115. SW114 Thrown = McKeesport.</t>
+          <t>Balloon connector (CO-3-dwarf). A48 east ends join: 120R/IH134 on McKeesport track protects Rocks / OS 115. SW114 Thrown = McKeesport.</t>
         </is>
       </c>
     </row>
@@ -17684,7 +17684,7 @@
       </c>
       <c r="Y80" t="inlineStr">
         <is>
-          <t>Balloon connector (SL-1-low). A48 east ends join: 120R/IH134 on McKeesport track protects Rocks / OS 115. SW114 Thrown = McKeesport.</t>
+          <t>Balloon connector (CO-3-dwarf). A48 east ends join: 120R/IH134 on McKeesport track protects Rocks / OS 115. SW114 Thrown = McKeesport.</t>
         </is>
       </c>
     </row>
@@ -17761,7 +17761,7 @@
       </c>
       <c r="Y81" t="inlineStr">
         <is>
-          <t>Balloon connector (SL-1-low). A48 east ends join: 120R/IH134 on McKeesport track protects Rocks / OS 115. SW114 Thrown = McKeesport.</t>
+          <t>Balloon connector (CO-3-dwarf). A48 east ends join: 120R/IH134 on McKeesport track protects Rocks / OS 115. SW114 Thrown = McKeesport.</t>
         </is>
       </c>
     </row>
@@ -17833,7 +17833,7 @@
       </c>
       <c r="Y82" t="inlineStr">
         <is>
-          <t>Balloon connector (SL-1-low). 120L/IH141 on Rocks track protects McKeesport / OS 114. SML also Stop if McKees Rocks occupied. SW115 Thrown = Rocks.</t>
+          <t>Balloon connector (CO-3-dwarf). 120L/IH141 on Rocks track protects McKeesport / OS 114. SML also Stop if McKees Rocks occupied. SW115 Thrown = Rocks.</t>
         </is>
       </c>
     </row>
@@ -17910,7 +17910,7 @@
       </c>
       <c r="Y83" t="inlineStr">
         <is>
-          <t>Balloon connector (SL-1-low). 120L/IH141 on Rocks track protects McKeesport / OS 114. SML also Stop if McKees Rocks occupied. SW115 Thrown = Rocks.</t>
+          <t>Balloon connector (CO-3-dwarf). 120L/IH141 on Rocks track protects McKeesport / OS 114. SML also Stop if McKees Rocks occupied. SW115 Thrown = Rocks.</t>
         </is>
       </c>
     </row>
@@ -17987,7 +17987,7 @@
       </c>
       <c r="Y84" t="inlineStr">
         <is>
-          <t>Balloon connector (SL-1-low). 120L/IH141 on Rocks track protects McKeesport / OS 114. SML also Stop if McKees Rocks occupied. SW115 Thrown = Rocks.</t>
+          <t>Balloon connector (CO-3-dwarf). 120L/IH141 on Rocks track protects McKeesport / OS 114. SML also Stop if McKees Rocks occupied. SW115 Thrown = Rocks.</t>
         </is>
       </c>
     </row>

--- a/cats/data/signals_asbuilt_abs_v2.xlsx
+++ b/cats/data/signals_asbuilt_abs_v2.xlsx
@@ -1815,7 +1815,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>C13-OU2-3 C13-OU2-1 C13-OU2-2 C13-OU2-6 C13-OU2-4 C13-OU2-5</t>
+          <t>C13-OU3-3 C13-OU3-1 C13-OU3-2 C13-OU3-6 C13-OU3-4 C13-OU3-5</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -1890,7 +1890,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>C13-OU4-7 C13-OU2-7 C13-OU2-8</t>
+          <t>C13-OU4-7 C13-OU3-7 C13-OU3-8</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
